--- a/Matar Trainings.xlsx
+++ b/Matar Trainings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l.karuru\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42DFFECE-210E-460F-86D9-350BFB8651EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72F4B6E8-5257-4DA6-B5C5-344DFDF46082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{2ACD8935-9A55-49F4-8AD3-9F8021E2249D}"/>
   </bookViews>
@@ -919,667 +919,667 @@
     <t>Norbert Mueller</t>
   </si>
   <si>
+    <t>Mohamed Farkan Mohamed Sareek</t>
+  </si>
+  <si>
+    <t>Destiny Emmanuel</t>
+  </si>
+  <si>
+    <t>Abdunaser Ahmed Aragaw</t>
+  </si>
+  <si>
+    <t>Rizardo Villalobos</t>
+  </si>
+  <si>
+    <t>Chidanand Bhaskara Chaithanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mahesh Ramachandra </t>
+  </si>
+  <si>
+    <t>Joel Cabrillos Misa</t>
+  </si>
+  <si>
+    <t>Ericson Murcillos Victorino</t>
+  </si>
+  <si>
+    <t>Fernan Dela Cruz</t>
+  </si>
+  <si>
+    <t>Bindu Pillai</t>
+  </si>
+  <si>
+    <t>Philippe Musangilay Kubula</t>
+  </si>
+  <si>
+    <t>Sandy De Vera Apigo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerry Arnejo Carandang </t>
+  </si>
+  <si>
+    <t>Vicente Mendigorin Morelos</t>
+  </si>
+  <si>
+    <t>Sivagaran Ramanathan</t>
+  </si>
+  <si>
+    <t>Cletes Albert Perera</t>
+  </si>
+  <si>
+    <t>Tharanga Pradeep Pathirannehelage</t>
+  </si>
+  <si>
+    <t>Pubudu Maduranga Hearth Ralalage</t>
+  </si>
+  <si>
+    <t>Joevergil Cajocson Dormitorio</t>
+  </si>
+  <si>
+    <t>Ricky Catibog Katigbak</t>
+  </si>
+  <si>
+    <t>Venice Mendova Jadloc</t>
+  </si>
+  <si>
+    <t>Lemuel Celeste Anacleto</t>
+  </si>
+  <si>
+    <t>Arnel Butiu Guevarra</t>
+  </si>
+  <si>
+    <t>Edwin Balakid Tegli</t>
+  </si>
+  <si>
+    <t>Jessie Jr. Alcuizar Hellera</t>
+  </si>
+  <si>
+    <t>Noel Jarabe Riego</t>
+  </si>
+  <si>
+    <t>Edilberto Angsioco</t>
+  </si>
+  <si>
+    <t>Jose Dino Constantino</t>
+  </si>
+  <si>
+    <t>Regin Alis</t>
+  </si>
+  <si>
+    <t>Restito Fabic</t>
+  </si>
+  <si>
+    <t>Kamalanathan Poopalapillai</t>
+  </si>
+  <si>
+    <t>Anil Kumara</t>
+  </si>
+  <si>
+    <t>Lani Fernando Kachchakaduge</t>
+  </si>
+  <si>
+    <t>Sampath Chamin</t>
+  </si>
+  <si>
+    <t>Raymond Ian Montero</t>
+  </si>
+  <si>
+    <t>James Magnaye Catapia</t>
+  </si>
+  <si>
+    <t>Marty Tolosa Ambas</t>
+  </si>
+  <si>
+    <t>Nove Manuel Menorisa Tagpuno</t>
+  </si>
+  <si>
+    <t>Edgar Noceja</t>
+  </si>
+  <si>
+    <t>Ma. Edelfa Mendoza</t>
+  </si>
+  <si>
+    <t>Mark Jayson Rosima</t>
+  </si>
+  <si>
+    <t>Cristopher Cruz</t>
+  </si>
+  <si>
+    <t>Ramanan Thavarasa</t>
+  </si>
+  <si>
+    <t>Renato Dimalanta Canlas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ruben Dela Cruz Malabo </t>
+  </si>
+  <si>
+    <t>Manuel Jr. Esplago Feniza</t>
+  </si>
+  <si>
+    <t>Billy Jim Morelos</t>
+  </si>
+  <si>
+    <t>Haren Del Campo</t>
+  </si>
+  <si>
+    <t>Mohamed Nabhan M. Shahiq</t>
+  </si>
+  <si>
+    <t>Rogelio Reyes Gomez Jr.</t>
+  </si>
+  <si>
+    <t>John Michael Yagonia</t>
+  </si>
+  <si>
+    <t>Ronnie Villanueva Gutierrez</t>
+  </si>
+  <si>
+    <t>Nenad Jovkovic</t>
+  </si>
+  <si>
+    <t>Nhuel Caguicla Landicho</t>
+  </si>
+  <si>
+    <t>Mohamed Riswan Mohamed Salyh</t>
+  </si>
+  <si>
+    <t>Dennis Ibe Sudario</t>
+  </si>
+  <si>
+    <t>Christian Archie Barbosa Niez</t>
+  </si>
+  <si>
+    <t>Clint Jude Duarte Bicoy</t>
+  </si>
+  <si>
+    <t>Willie Facun Adi</t>
+  </si>
+  <si>
+    <t>Eduard Embate Endonela</t>
+  </si>
+  <si>
+    <t>Sugathadasa Pattiwilage</t>
+  </si>
+  <si>
+    <t>Gomer Repaso Plenos</t>
+  </si>
+  <si>
+    <t>John Errol Para Marino</t>
+  </si>
+  <si>
+    <t>Gabuin James Buintim</t>
+  </si>
+  <si>
+    <t>Marlon Rodel Fracisco Pimentel</t>
+  </si>
+  <si>
+    <t>Nathaniel Laguidao Gamosa</t>
+  </si>
+  <si>
+    <t>Ernesto JR Leona Campana</t>
+  </si>
+  <si>
+    <t>William Villanueva Gutierrez</t>
+  </si>
+  <si>
+    <t>Conrado DE Guzman Vineza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elecer Hernandez Llamoso </t>
+  </si>
+  <si>
+    <t>Elesor JR Cas Frondozo</t>
+  </si>
+  <si>
+    <t>Carlo Alcoran Tenorio</t>
+  </si>
+  <si>
+    <t>Alvin Quizon Tabasa</t>
+  </si>
+  <si>
+    <t>Miguelito Costelo Mainit</t>
+  </si>
+  <si>
+    <t>Mohamed Nasardeen Mohamadu Main</t>
+  </si>
+  <si>
+    <t>Dominic Munyua Kanyotu</t>
+  </si>
+  <si>
+    <t>Lenson Kiarie Karuru</t>
+  </si>
+  <si>
+    <t>Ryan Mauring Adol</t>
+  </si>
+  <si>
+    <t>Joey JR Tiwo Meramonte</t>
+  </si>
+  <si>
+    <t>Mario Dorado Hernandez</t>
+  </si>
+  <si>
+    <t>Sooraj Kurisinkal Reji</t>
+  </si>
+  <si>
+    <t>Jose Isagani Jr. Jamero Alaan</t>
+  </si>
+  <si>
+    <t>Jishnu Surendran</t>
+  </si>
+  <si>
+    <t>Saritha Oromariyil Sukumaran</t>
+  </si>
+  <si>
+    <t>Renz Jake Orense Lontoc</t>
+  </si>
+  <si>
+    <t>Dennis Delfino Daginotan</t>
+  </si>
+  <si>
+    <t>John Eric Bonganay Borcelis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ray Maitem Maureal </t>
+  </si>
+  <si>
+    <t>Paul Jeric Azul Falcatan</t>
+  </si>
+  <si>
+    <t>Roderick Cailao Amar</t>
+  </si>
+  <si>
+    <t>Jimmy Mallari Dela Cruz</t>
+  </si>
+  <si>
+    <t>Meegle Mathew</t>
+  </si>
+  <si>
+    <t>Thuvarakan Pulenthiran</t>
+  </si>
+  <si>
+    <t>Jerome Latagan Cardejon</t>
+  </si>
+  <si>
+    <t>Jay Tucker Mendoza</t>
+  </si>
+  <si>
+    <t>Crisfo Lo Nibal</t>
+  </si>
+  <si>
+    <t>Simon Kenneth Inoceno Hernandez</t>
+  </si>
+  <si>
+    <t>Levitico Jose Caniedo</t>
+  </si>
+  <si>
+    <t>Mohamed Faizal Mohamed Uvais</t>
+  </si>
+  <si>
+    <t>Nhar Jaradal Cillo</t>
+  </si>
+  <si>
+    <t>Herwin Fatalla Mimay</t>
+  </si>
+  <si>
+    <t>Nino Vercide Arda</t>
+  </si>
+  <si>
+    <t>Jason Puzon Dy</t>
+  </si>
+  <si>
+    <t>Rholie Pacio Casison</t>
+  </si>
+  <si>
+    <t>Jeffrey Manarpaac Urolaza</t>
+  </si>
+  <si>
+    <t>Edison Mendoza Rojas</t>
+  </si>
+  <si>
+    <t>Mark Merill Jovenes Tirol</t>
+  </si>
+  <si>
+    <t>Kennedy Gichuhi Ngaruiya</t>
+  </si>
+  <si>
+    <t>Francis Agbor Eyong Atem</t>
+  </si>
+  <si>
+    <t>Siraj Moolakkappil</t>
+  </si>
+  <si>
+    <t>Mohamed Bilal Muneer Basha</t>
+  </si>
+  <si>
+    <t>Alen Cherippanat Babu</t>
+  </si>
+  <si>
+    <t>Mohamed Shafras Jawlangull</t>
+  </si>
+  <si>
+    <t>Renson Gicheha Gicheru</t>
+  </si>
+  <si>
+    <t>Mohamed Faris Mohamed Naleem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shihabdeen Seeni Mohamed </t>
+  </si>
+  <si>
+    <t>Prakyath Prabhakar Amin</t>
+  </si>
+  <si>
+    <t>Julius Kateregga</t>
+  </si>
+  <si>
+    <t>Kishanraj Pulenthiran</t>
+  </si>
+  <si>
+    <t>James Kariungi Muthee</t>
+  </si>
+  <si>
+    <t>Kasansula Francis Kiwanuka</t>
+  </si>
+  <si>
+    <t>Arnel Neri Montemayor</t>
+  </si>
+  <si>
+    <t>Erick Omondi Okoyo</t>
+  </si>
+  <si>
+    <t>Trevin Christopher Neydorf</t>
+  </si>
+  <si>
+    <t>Mohamed Mufaris Mohamed Jameel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jasim Kinarullaparambath Kunhabdulla </t>
+  </si>
+  <si>
+    <t>Naser Qasim Mohammad Alhaj Ahmed</t>
+  </si>
+  <si>
+    <t>Jeffrey Sayson Bagatua</t>
+  </si>
+  <si>
+    <t>Wali Mohammed Sabry</t>
+  </si>
+  <si>
+    <t>Rommel Tamayo Eleosida</t>
+  </si>
+  <si>
+    <t>Errolnil Purificacion Atienza</t>
+  </si>
+  <si>
+    <t>Hernan John Baguion Murcillos</t>
+  </si>
+  <si>
+    <t>Ivan Raphael Macatangay Del Mundo</t>
+  </si>
+  <si>
+    <t>Jerico Tallorin Atienzo</t>
+  </si>
+  <si>
+    <t>Alvin Tumboc Cuevas</t>
+  </si>
+  <si>
+    <t>James Andrew Aquino Rodillo</t>
+  </si>
+  <si>
+    <t>Alvin Cataquiz Austria</t>
+  </si>
+  <si>
+    <t>Jayson Ruz Oligan</t>
+  </si>
+  <si>
+    <t>John Michael Angelo Mesina Clemen</t>
+  </si>
+  <si>
+    <t>Lemuel Carcellar Macatangay</t>
+  </si>
+  <si>
+    <t>Nikko Villanueva Cruz</t>
+  </si>
+  <si>
+    <t>Justin Paolo Macatangay Ilao</t>
+  </si>
+  <si>
+    <t>Jake Alinabon Salibay</t>
+  </si>
+  <si>
+    <t>Marlon Yuson Pamplona</t>
+  </si>
+  <si>
+    <t>Joe Vergil Jr Calanza Dormitorio</t>
+  </si>
+  <si>
+    <t>Bonifacio Arano Bayer</t>
+  </si>
+  <si>
+    <t>Sumedha Pradeep Dissanayaka</t>
+  </si>
+  <si>
+    <t>Yuvashanth Somasuntharam kukasuthan</t>
+  </si>
+  <si>
+    <t>Jonel Catibog Katigbak</t>
+  </si>
+  <si>
+    <t>Catalino Mendoza Rojas</t>
+  </si>
+  <si>
+    <t>Murshidul Haq Patteri Thazhe Kuni</t>
+  </si>
+  <si>
+    <t>Nisham Kizhakke Valappil</t>
+  </si>
+  <si>
+    <t>Pasidu Pamodaya Rathnayake Rathnayake Mudiyanselage</t>
+  </si>
+  <si>
+    <t>Chalana Ishan Dishanayake Dishanayake Pathiranage</t>
+  </si>
+  <si>
+    <t>Mohamed Ahthir Abdul Majeed</t>
+  </si>
+  <si>
+    <t>Niroshan Abesingha Abesingha Karunarathna Mudalige</t>
+  </si>
+  <si>
+    <t>Sathis Gunawardhana Dikella Kandha Yakdhehirallage</t>
+  </si>
+  <si>
+    <t>Tharaka Thanujaya Dissanayaka Dissanayaka Mudiyanselage</t>
+  </si>
+  <si>
+    <t>Nishan Ekanayake Ekanayake Mudiyanselage</t>
+  </si>
+  <si>
+    <t>Jacky Chan Nava Gastardo</t>
+  </si>
+  <si>
+    <t>Mohammed Fahim Mohammed Laffir</t>
+  </si>
+  <si>
+    <t>Sameera Lakmal Rupasinghe Arachchige</t>
+  </si>
+  <si>
+    <t>Dushan Priyankara Herath Herath Mudiyanselage</t>
+  </si>
+  <si>
+    <t>Pathmapriyan Muruguppilla</t>
+  </si>
+  <si>
+    <t>Roshan Chaminda Udawaththa Udawaththa Kankanamge</t>
+  </si>
+  <si>
+    <t>Kusal Sharmila Hewa Kokawalage</t>
+  </si>
+  <si>
+    <t>Mohomed Minnas Mohomed Ramees</t>
+  </si>
+  <si>
+    <t>Mabin Pauly</t>
+  </si>
+  <si>
+    <t>Jahsim Saycon Apila</t>
+  </si>
+  <si>
+    <t>Shern Sebastian Sebastian Simon</t>
+  </si>
+  <si>
+    <t>Wai Hin Phyo</t>
+  </si>
+  <si>
+    <t>Hicham Charkaoui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mohamed Shaheer Mohamed Laffir </t>
+  </si>
+  <si>
+    <t>Antony Kamau Kageche</t>
+  </si>
+  <si>
+    <t>Abdulrashid Byarugaba </t>
+  </si>
+  <si>
+    <t>Justine Tiangson Clave</t>
+  </si>
+  <si>
+    <t>Harikaran Seenithamby</t>
+  </si>
+  <si>
+    <t>Wycliffe Mushori</t>
+  </si>
+  <si>
+    <t>Peter Nganga Kamau</t>
+  </si>
+  <si>
+    <t>Sumesh Soman</t>
+  </si>
+  <si>
+    <t>Muhammed Ashiq Mohamed Mumtaz</t>
+  </si>
+  <si>
+    <t>Arvin Clyde D.Crisme</t>
+  </si>
+  <si>
+    <t>Gary John Packer</t>
+  </si>
+  <si>
+    <t>Ifras Mohammed</t>
+  </si>
+  <si>
+    <t>Alby Manchandiyil Antony</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ifran Ansari </t>
+  </si>
+  <si>
+    <t>Piratheepan Thiyagarasa</t>
+  </si>
+  <si>
+    <t>Moustafa Hassan Ibrahim Elsayyad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harsha Shetty </t>
+  </si>
+  <si>
+    <t>Kevin Carl Enriquez Serrano</t>
+  </si>
+  <si>
+    <t>Romie Ross Tamayo Eleosida</t>
+  </si>
+  <si>
+    <t>Quennan Carandang Cuesta</t>
+  </si>
+  <si>
+    <t>Lester John Fuentes Monter</t>
+  </si>
+  <si>
+    <t>Neil Jhon Sabile Ramos</t>
+  </si>
+  <si>
+    <t>Kim Harvey Cuevas Ayag</t>
+  </si>
+  <si>
+    <t>Nelson Jr Ybut Sancho</t>
+  </si>
+  <si>
+    <t>Rolly Miano Valdez</t>
+  </si>
+  <si>
+    <t>Daniel Bacolcol Orquiza</t>
+  </si>
+  <si>
+    <t>Roby Chua Malinao</t>
+  </si>
+  <si>
+    <t>Lorence Cardenas Cabales</t>
+  </si>
+  <si>
+    <t>Emmanuel Richard Marasigan Velasco</t>
+  </si>
+  <si>
+    <t>Michael Jorge Toscano Masaoy</t>
+  </si>
+  <si>
+    <t>Jeffrey De Vera Cabico</t>
+  </si>
+  <si>
+    <t>Joe Peter Angustia Pimentel</t>
+  </si>
+  <si>
+    <t>Mark Roentgen Macatangay Delen</t>
+  </si>
+  <si>
+    <t>Arjay Imperial Gabarda</t>
+  </si>
+  <si>
+    <t>Noey Francisco Canonizado</t>
+  </si>
+  <si>
+    <t>Omar Zaki Saad Abdel Nabi</t>
+  </si>
+  <si>
+    <t>Abdul Rehman Mohammed Abdul Mohammed</t>
+  </si>
+  <si>
+    <t>Christian Merck Morada Martija</t>
+  </si>
+  <si>
+    <t>Imesha Rashmi Mudannayaka Mudannayakage</t>
+  </si>
+  <si>
+    <t>Sajith Dulanjana Kumara Rathnayaka Mudiyanselage</t>
+  </si>
+  <si>
+    <t>Thisura Kaumal Wijesinghe</t>
+  </si>
+  <si>
+    <t>Shanel Rukshan Perera Kurana Patabendige</t>
+  </si>
+  <si>
+    <t>Abeykoon Mudiyanselage Sasitha Dinushka Abeykoon</t>
+  </si>
+  <si>
+    <t>Jerusha Anns Philip</t>
+  </si>
+  <si>
     <t>Management</t>
   </si>
   <si>
-    <t>Mohamed Farkan Mohamed Sareek</t>
-  </si>
-  <si>
-    <t>Destiny Emmanuel</t>
-  </si>
-  <si>
-    <t>Abdunaser Ahmed Aragaw</t>
-  </si>
-  <si>
     <t>CARGO CM</t>
   </si>
   <si>
-    <t>Rizardo Villalobos</t>
-  </si>
-  <si>
-    <t>Chidanand Bhaskara Chaithanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mahesh Ramachandra </t>
-  </si>
-  <si>
     <t>CARGO PM</t>
   </si>
   <si>
-    <t>Joel Cabrillos Misa</t>
-  </si>
-  <si>
-    <t>Ericson Murcillos Victorino</t>
-  </si>
-  <si>
-    <t>Fernan Dela Cruz</t>
-  </si>
-  <si>
-    <t>Bindu Pillai</t>
-  </si>
-  <si>
-    <t>Philippe Musangilay Kubula</t>
-  </si>
-  <si>
-    <t>Sandy De Vera Apigo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerry Arnejo Carandang </t>
-  </si>
-  <si>
-    <t>Vicente Mendigorin Morelos</t>
-  </si>
-  <si>
-    <t>Sivagaran Ramanathan</t>
-  </si>
-  <si>
-    <t>Cletes Albert Perera</t>
-  </si>
-  <si>
-    <t>Tharanga Pradeep Pathirannehelage</t>
-  </si>
-  <si>
-    <t>Pubudu Maduranga Hearth Ralalage</t>
-  </si>
-  <si>
-    <t>Joevergil Cajocson Dormitorio</t>
-  </si>
-  <si>
-    <t>Ricky Catibog Katigbak</t>
-  </si>
-  <si>
-    <t>Venice Mendova Jadloc</t>
-  </si>
-  <si>
-    <t>Lemuel Celeste Anacleto</t>
-  </si>
-  <si>
-    <t>Arnel Butiu Guevarra</t>
-  </si>
-  <si>
-    <t>Edwin Balakid Tegli</t>
-  </si>
-  <si>
-    <t>Jessie Jr. Alcuizar Hellera</t>
-  </si>
-  <si>
-    <t>Noel Jarabe Riego</t>
-  </si>
-  <si>
-    <t>Edilberto Angsioco</t>
-  </si>
-  <si>
-    <t>Jose Dino Constantino</t>
-  </si>
-  <si>
-    <t>Regin Alis</t>
-  </si>
-  <si>
-    <t>Restito Fabic</t>
-  </si>
-  <si>
-    <t>Kamalanathan Poopalapillai</t>
-  </si>
-  <si>
-    <t>Anil Kumara</t>
-  </si>
-  <si>
-    <t>Lani Fernando Kachchakaduge</t>
-  </si>
-  <si>
-    <t>Sampath Chamin</t>
-  </si>
-  <si>
-    <t>Raymond Ian Montero</t>
-  </si>
-  <si>
-    <t>James Magnaye Catapia</t>
-  </si>
-  <si>
-    <t>Marty Tolosa Ambas</t>
-  </si>
-  <si>
-    <t>Nove Manuel Menorisa Tagpuno</t>
-  </si>
-  <si>
-    <t>Edgar Noceja</t>
-  </si>
-  <si>
-    <t>Ma. Edelfa Mendoza</t>
-  </si>
-  <si>
-    <t>Mark Jayson Rosima</t>
-  </si>
-  <si>
-    <t>Cristopher Cruz</t>
-  </si>
-  <si>
-    <t>Ramanan Thavarasa</t>
-  </si>
-  <si>
-    <t>Renato Dimalanta Canlas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ruben Dela Cruz Malabo </t>
-  </si>
-  <si>
-    <t>Manuel Jr. Esplago Feniza</t>
-  </si>
-  <si>
-    <t>Billy Jim Morelos</t>
-  </si>
-  <si>
-    <t>Haren Del Campo</t>
-  </si>
-  <si>
-    <t>Mohamed Nabhan M. Shahiq</t>
-  </si>
-  <si>
-    <t>Rogelio Reyes Gomez Jr.</t>
-  </si>
-  <si>
-    <t>John Michael Yagonia</t>
-  </si>
-  <si>
-    <t>Ronnie Villanueva Gutierrez</t>
-  </si>
-  <si>
-    <t>Nenad Jovkovic</t>
-  </si>
-  <si>
-    <t>Nhuel Caguicla Landicho</t>
-  </si>
-  <si>
-    <t>Mohamed Riswan Mohamed Salyh</t>
-  </si>
-  <si>
-    <t>Dennis Ibe Sudario</t>
-  </si>
-  <si>
-    <t>Christian Archie Barbosa Niez</t>
-  </si>
-  <si>
-    <t>Clint Jude Duarte Bicoy</t>
-  </si>
-  <si>
-    <t>Willie Facun Adi</t>
-  </si>
-  <si>
-    <t>Eduard Embate Endonela</t>
-  </si>
-  <si>
-    <t>Sugathadasa Pattiwilage</t>
-  </si>
-  <si>
-    <t>Gomer Repaso Plenos</t>
-  </si>
-  <si>
-    <t>John Errol Para Marino</t>
-  </si>
-  <si>
-    <t>Gabuin James Buintim</t>
-  </si>
-  <si>
-    <t>Marlon Rodel Fracisco Pimentel</t>
-  </si>
-  <si>
-    <t>Nathaniel Laguidao Gamosa</t>
-  </si>
-  <si>
-    <t>Ernesto JR Leona Campana</t>
-  </si>
-  <si>
-    <t>William Villanueva Gutierrez</t>
-  </si>
-  <si>
-    <t>Conrado DE Guzman Vineza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elecer Hernandez Llamoso </t>
-  </si>
-  <si>
-    <t>Elesor JR Cas Frondozo</t>
-  </si>
-  <si>
-    <t>Carlo Alcoran Tenorio</t>
-  </si>
-  <si>
-    <t>Alvin Quizon Tabasa</t>
-  </si>
-  <si>
-    <t>Miguelito Costelo Mainit</t>
-  </si>
-  <si>
-    <t>Mohamed Nasardeen Mohamadu Main</t>
-  </si>
-  <si>
-    <t>Dominic Munyua Kanyotu</t>
-  </si>
-  <si>
-    <t>Lenson Kiarie Karuru</t>
-  </si>
-  <si>
-    <t>Ryan Mauring Adol</t>
-  </si>
-  <si>
-    <t>Joey JR Tiwo Meramonte</t>
-  </si>
-  <si>
-    <t>Mario Dorado Hernandez</t>
-  </si>
-  <si>
-    <t>Sooraj Kurisinkal Reji</t>
-  </si>
-  <si>
     <t>IT/PLC</t>
   </si>
   <si>
-    <t>Jose Isagani Jr. Jamero Alaan</t>
-  </si>
-  <si>
-    <t>Jishnu Surendran</t>
-  </si>
-  <si>
-    <t>Saritha Oromariyil Sukumaran</t>
-  </si>
-  <si>
-    <t>Renz Jake Orense Lontoc</t>
-  </si>
-  <si>
-    <t>Dennis Delfino Daginotan</t>
-  </si>
-  <si>
-    <t>John Eric Bonganay Borcelis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ray Maitem Maureal </t>
-  </si>
-  <si>
-    <t>Paul Jeric Azul Falcatan</t>
-  </si>
-  <si>
-    <t>Roderick Cailao Amar</t>
-  </si>
-  <si>
-    <t>Jimmy Mallari Dela Cruz</t>
-  </si>
-  <si>
-    <t>Meegle Mathew</t>
-  </si>
-  <si>
-    <t>Thuvarakan Pulenthiran</t>
-  </si>
-  <si>
-    <t>Jerome Latagan Cardejon</t>
-  </si>
-  <si>
-    <t>Jay Tucker Mendoza</t>
-  </si>
-  <si>
-    <t>Crisfo Lo Nibal</t>
-  </si>
-  <si>
-    <t>Simon Kenneth Inoceno Hernandez</t>
-  </si>
-  <si>
-    <t>Levitico Jose Caniedo</t>
-  </si>
-  <si>
-    <t>Mohamed Faizal Mohamed Uvais</t>
-  </si>
-  <si>
-    <t>Nhar Jaradal Cillo</t>
-  </si>
-  <si>
-    <t>Herwin Fatalla Mimay</t>
-  </si>
-  <si>
-    <t>Nino Vercide Arda</t>
-  </si>
-  <si>
-    <t>Jason Puzon Dy</t>
-  </si>
-  <si>
-    <t>Rholie Pacio Casison</t>
-  </si>
-  <si>
-    <t>Jeffrey Manarpaac Urolaza</t>
-  </si>
-  <si>
-    <t>Edison Mendoza Rojas</t>
-  </si>
-  <si>
-    <t>Mark Merill Jovenes Tirol</t>
-  </si>
-  <si>
-    <t>Kennedy Gichuhi Ngaruiya</t>
-  </si>
-  <si>
-    <t>Francis Agbor Eyong Atem</t>
-  </si>
-  <si>
-    <t>Siraj Moolakkappil</t>
-  </si>
-  <si>
-    <t>Mohamed Bilal Muneer Basha</t>
-  </si>
-  <si>
-    <t>Alen Cherippanat Babu</t>
-  </si>
-  <si>
-    <t>Mohamed Shafras Jawlangull</t>
-  </si>
-  <si>
-    <t>Renson Gicheha Gicheru</t>
-  </si>
-  <si>
-    <t>Mohamed Faris Mohamed Naleem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shihabdeen Seeni Mohamed </t>
-  </si>
-  <si>
-    <t>Prakyath Prabhakar Amin</t>
-  </si>
-  <si>
-    <t>Julius Kateregga</t>
-  </si>
-  <si>
-    <t>Kishanraj Pulenthiran</t>
-  </si>
-  <si>
-    <t>James Kariungi Muthee</t>
-  </si>
-  <si>
-    <t>Kasansula Francis Kiwanuka</t>
-  </si>
-  <si>
-    <t>Arnel Neri Montemayor</t>
-  </si>
-  <si>
-    <t>Erick Omondi Okoyo</t>
-  </si>
-  <si>
-    <t>Trevin Christopher Neydorf</t>
-  </si>
-  <si>
-    <t>Mohamed Mufaris Mohamed Jameel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jasim Kinarullaparambath Kunhabdulla </t>
-  </si>
-  <si>
-    <t>Naser Qasim Mohammad Alhaj Ahmed</t>
-  </si>
-  <si>
-    <t>Jeffrey Sayson Bagatua</t>
-  </si>
-  <si>
-    <t>Wali Mohammed Sabry</t>
-  </si>
-  <si>
-    <t>Rommel Tamayo Eleosida</t>
-  </si>
-  <si>
-    <t>Errolnil Purificacion Atienza</t>
-  </si>
-  <si>
-    <t>Hernan John Baguion Murcillos</t>
-  </si>
-  <si>
-    <t>Ivan Raphael Macatangay Del Mundo</t>
-  </si>
-  <si>
-    <t>Jerico Tallorin Atienzo</t>
-  </si>
-  <si>
-    <t>Alvin Tumboc Cuevas</t>
-  </si>
-  <si>
-    <t>James Andrew Aquino Rodillo</t>
-  </si>
-  <si>
-    <t>Alvin Cataquiz Austria</t>
-  </si>
-  <si>
-    <t>Jayson Ruz Oligan</t>
-  </si>
-  <si>
-    <t>John Michael Angelo Mesina Clemen</t>
-  </si>
-  <si>
-    <t>Lemuel Carcellar Macatangay</t>
-  </si>
-  <si>
-    <t>Nikko Villanueva Cruz</t>
-  </si>
-  <si>
-    <t>Justin Paolo Macatangay Ilao</t>
-  </si>
-  <si>
-    <t>Jake Alinabon Salibay</t>
-  </si>
-  <si>
-    <t>Marlon Yuson Pamplona</t>
-  </si>
-  <si>
-    <t>Joe Vergil Jr Calanza Dormitorio</t>
-  </si>
-  <si>
-    <t>Bonifacio Arano Bayer</t>
-  </si>
-  <si>
-    <t>Sumedha Pradeep Dissanayaka</t>
-  </si>
-  <si>
-    <t>Yuvashanth Somasuntharam kukasuthan</t>
-  </si>
-  <si>
-    <t>Jonel Catibog Katigbak</t>
-  </si>
-  <si>
-    <t>Catalino Mendoza Rojas</t>
-  </si>
-  <si>
-    <t>Murshidul Haq Patteri Thazhe Kuni</t>
-  </si>
-  <si>
-    <t>Nisham Kizhakke Valappil</t>
-  </si>
-  <si>
-    <t>Pasidu Pamodaya Rathnayake Rathnayake Mudiyanselage</t>
-  </si>
-  <si>
-    <t>Chalana Ishan Dishanayake Dishanayake Pathiranage</t>
-  </si>
-  <si>
-    <t>Mohamed Ahthir Abdul Majeed</t>
-  </si>
-  <si>
-    <t>Niroshan Abesingha Abesingha Karunarathna Mudalige</t>
-  </si>
-  <si>
-    <t>Sathis Gunawardhana Dikella Kandha Yakdhehirallage</t>
-  </si>
-  <si>
-    <t>Tharaka Thanujaya Dissanayaka Dissanayaka Mudiyanselage</t>
-  </si>
-  <si>
-    <t>Nishan Ekanayake Ekanayake Mudiyanselage</t>
-  </si>
-  <si>
-    <t>Jacky Chan Nava Gastardo</t>
-  </si>
-  <si>
-    <t>Mohammed Fahim Mohammed Laffir</t>
-  </si>
-  <si>
-    <t>Sameera Lakmal Rupasinghe Arachchige</t>
-  </si>
-  <si>
-    <t>Dushan Priyankara Herath Herath Mudiyanselage</t>
-  </si>
-  <si>
-    <t>Pathmapriyan Muruguppilla</t>
-  </si>
-  <si>
-    <t>Roshan Chaminda Udawaththa Udawaththa Kankanamge</t>
-  </si>
-  <si>
-    <t>Kusal Sharmila Hewa Kokawalage</t>
-  </si>
-  <si>
-    <t>Mohomed Minnas Mohomed Ramees</t>
-  </si>
-  <si>
-    <t>Mabin Pauly</t>
-  </si>
-  <si>
-    <t>Jahsim Saycon Apila</t>
-  </si>
-  <si>
-    <t>Shern Sebastian Sebastian Simon</t>
-  </si>
-  <si>
-    <t>Wai Hin Phyo</t>
-  </si>
-  <si>
-    <t>Hicham Charkaoui</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mohamed Shaheer Mohamed Laffir </t>
-  </si>
-  <si>
-    <t>Antony Kamau Kageche</t>
-  </si>
-  <si>
-    <t>Abdulrashid Byarugaba </t>
-  </si>
-  <si>
-    <t>Justine Tiangson Clave</t>
-  </si>
-  <si>
-    <t>Harikaran Seenithamby</t>
-  </si>
-  <si>
-    <t>Wycliffe Mushori</t>
-  </si>
-  <si>
-    <t>Peter Nganga Kamau</t>
-  </si>
-  <si>
-    <t>Sumesh Soman</t>
-  </si>
-  <si>
-    <t>Muhammed Ashiq Mohamed Mumtaz</t>
-  </si>
-  <si>
-    <t>Arvin Clyde D.Crisme</t>
-  </si>
-  <si>
-    <t>Gary John Packer</t>
-  </si>
-  <si>
-    <t>Ifras Mohammed</t>
-  </si>
-  <si>
-    <t>Alby Manchandiyil Antony</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ifran Ansari </t>
-  </si>
-  <si>
-    <t>Piratheepan Thiyagarasa</t>
-  </si>
-  <si>
-    <t>Moustafa Hassan Ibrahim Elsayyad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harsha Shetty </t>
-  </si>
-  <si>
-    <t>Kevin Carl Enriquez Serrano</t>
-  </si>
-  <si>
-    <t>Romie Ross Tamayo Eleosida</t>
-  </si>
-  <si>
-    <t>Quennan Carandang Cuesta</t>
-  </si>
-  <si>
     <t>U5</t>
-  </si>
-  <si>
-    <t>Lester John Fuentes Monter</t>
-  </si>
-  <si>
-    <t>Neil Jhon Sabile Ramos</t>
-  </si>
-  <si>
-    <t>Kim Harvey Cuevas Ayag</t>
-  </si>
-  <si>
-    <t>Nelson Jr Ybut Sancho</t>
-  </si>
-  <si>
-    <t>Rolly Miano Valdez</t>
-  </si>
-  <si>
-    <t>Daniel Bacolcol Orquiza</t>
-  </si>
-  <si>
-    <t>Roby Chua Malinao</t>
-  </si>
-  <si>
-    <t>Lorence Cardenas Cabales</t>
-  </si>
-  <si>
-    <t>Emmanuel Richard Marasigan Velasco</t>
-  </si>
-  <si>
-    <t>Michael Jorge Toscano Masaoy</t>
-  </si>
-  <si>
-    <t>Jeffrey De Vera Cabico</t>
-  </si>
-  <si>
-    <t>Joe Peter Angustia Pimentel</t>
-  </si>
-  <si>
-    <t>Mark Roentgen Macatangay Delen</t>
-  </si>
-  <si>
-    <t>Arjay Imperial Gabarda</t>
-  </si>
-  <si>
-    <t>Noey Francisco Canonizado</t>
-  </si>
-  <si>
-    <t>Omar Zaki Saad Abdel Nabi</t>
-  </si>
-  <si>
-    <t>Abdul Rehman Mohammed Abdul Mohammed</t>
-  </si>
-  <si>
-    <t>Christian Merck Morada Martija</t>
-  </si>
-  <si>
-    <t>Imesha Rashmi Mudannayaka Mudannayakage</t>
-  </si>
-  <si>
-    <t>Sajith Dulanjana Kumara Rathnayaka Mudiyanselage</t>
-  </si>
-  <si>
-    <t>Thisura Kaumal Wijesinghe</t>
-  </si>
-  <si>
-    <t>Shanel Rukshan Perera Kurana Patabendige</t>
-  </si>
-  <si>
-    <t>Abeykoon Mudiyanselage Sasitha Dinushka Abeykoon</t>
-  </si>
-  <si>
-    <t>Jerusha Anns Philip</t>
   </si>
 </sst>
 </file>
@@ -2090,7 +2090,7 @@
         <v>245</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>291</v>
+        <v>507</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
@@ -2104,7 +2104,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>246</v>
@@ -2124,7 +2124,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>247</v>
@@ -2144,13 +2144,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>248</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>295</v>
+        <v>508</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>232</v>
@@ -2166,13 +2166,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>249</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>295</v>
+        <v>508</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>232</v>
@@ -2188,7 +2188,7 @@
         <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>250</v>
@@ -2208,13 +2208,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>251</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>232</v>
@@ -2230,13 +2230,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>252</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>295</v>
+        <v>508</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>232</v>
@@ -2252,7 +2252,7 @@
         <v>12</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>247</v>
@@ -2272,13 +2272,13 @@
         <v>13</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>251</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>232</v>
@@ -2294,13 +2294,13 @@
         <v>14</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>251</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>291</v>
+        <v>507</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
@@ -2314,7 +2314,7 @@
         <v>15</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>246</v>
@@ -2334,13 +2334,13 @@
         <v>16</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>253</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>295</v>
+        <v>508</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>232</v>
@@ -2356,13 +2356,13 @@
         <v>17</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>251</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>232</v>
@@ -2378,7 +2378,7 @@
         <v>18</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>254</v>
@@ -2398,13 +2398,13 @@
         <v>19</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>255</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>232</v>
@@ -2420,13 +2420,13 @@
         <v>20</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>256</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>232</v>
@@ -2442,13 +2442,13 @@
         <v>21</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>248</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>295</v>
+        <v>508</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>232</v>
@@ -2464,13 +2464,13 @@
         <v>22</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>255</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>232</v>
@@ -2486,13 +2486,13 @@
         <v>23</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>248</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>295</v>
+        <v>508</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>232</v>
@@ -2508,7 +2508,7 @@
         <v>24</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>257</v>
@@ -2528,7 +2528,7 @@
         <v>25</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>254</v>
@@ -2548,13 +2548,13 @@
         <v>26</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>252</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>295</v>
+        <v>508</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>232</v>
@@ -2570,13 +2570,13 @@
         <v>27</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>249</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>295</v>
+        <v>508</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>232</v>
@@ -2592,7 +2592,7 @@
         <v>28</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>254</v>
@@ -2612,7 +2612,7 @@
         <v>29</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>246</v>
@@ -2632,7 +2632,7 @@
         <v>30</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>254</v>
@@ -2652,13 +2652,13 @@
         <v>31</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>248</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>295</v>
+        <v>508</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>232</v>
@@ -2674,7 +2674,7 @@
         <v>32</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>246</v>
@@ -2694,13 +2694,13 @@
         <v>33</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>249</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>295</v>
+        <v>508</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>232</v>
@@ -2716,7 +2716,7 @@
         <v>34</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>246</v>
@@ -2736,7 +2736,7 @@
         <v>35</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>258</v>
@@ -2756,7 +2756,7 @@
         <v>36</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>258</v>
@@ -2776,13 +2776,13 @@
         <v>37</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>255</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>232</v>
@@ -2798,13 +2798,13 @@
         <v>38</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>259</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>232</v>
@@ -2820,7 +2820,7 @@
         <v>39</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>260</v>
@@ -2840,13 +2840,13 @@
         <v>40</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>252</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>295</v>
+        <v>508</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>232</v>
@@ -2862,7 +2862,7 @@
         <v>41</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>254</v>
@@ -2882,13 +2882,13 @@
         <v>42</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>253</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>295</v>
+        <v>508</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>232</v>
@@ -2904,13 +2904,13 @@
         <v>43</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>253</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>295</v>
+        <v>508</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>232</v>
@@ -2926,7 +2926,7 @@
         <v>44</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>246</v>
@@ -2946,7 +2946,7 @@
         <v>45</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>254</v>
@@ -2966,7 +2966,7 @@
         <v>46</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>261</v>
@@ -2986,7 +2986,7 @@
         <v>47</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>258</v>
@@ -3006,7 +3006,7 @@
         <v>48</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>262</v>
@@ -3026,7 +3026,7 @@
         <v>49</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>262</v>
@@ -3046,7 +3046,7 @@
         <v>50</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>247</v>
@@ -3066,7 +3066,7 @@
         <v>51</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>262</v>
@@ -3086,7 +3086,7 @@
         <v>52</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>247</v>
@@ -3106,7 +3106,7 @@
         <v>53</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>261</v>
@@ -3126,7 +3126,7 @@
         <v>54</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>262</v>
@@ -3146,7 +3146,7 @@
         <v>55</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>263</v>
@@ -3166,13 +3166,13 @@
         <v>56</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>251</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>232</v>
@@ -3188,13 +3188,13 @@
         <v>57</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>245</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>291</v>
+        <v>507</v>
       </c>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
@@ -3208,7 +3208,7 @@
         <v>58</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>250</v>
@@ -3228,13 +3228,13 @@
         <v>59</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>264</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>232</v>
@@ -3250,13 +3250,13 @@
         <v>60</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>253</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>295</v>
+        <v>508</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>232</v>
@@ -3272,13 +3272,13 @@
         <v>61</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>253</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>295</v>
+        <v>508</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>232</v>
@@ -3294,13 +3294,13 @@
         <v>62</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>252</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>295</v>
+        <v>508</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>232</v>
@@ -3316,7 +3316,7 @@
         <v>63</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>257</v>
@@ -3336,7 +3336,7 @@
         <v>64</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>254</v>
@@ -3356,13 +3356,13 @@
         <v>65</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>256</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>232</v>
@@ -3378,13 +3378,13 @@
         <v>66</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>249</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>295</v>
+        <v>508</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>232</v>
@@ -3400,7 +3400,7 @@
         <v>67</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>257</v>
@@ -3420,7 +3420,7 @@
         <v>68</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>246</v>
@@ -3440,7 +3440,7 @@
         <v>69</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>247</v>
@@ -3460,7 +3460,7 @@
         <v>70</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>263</v>
@@ -3480,7 +3480,7 @@
         <v>71</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>257</v>
@@ -3500,7 +3500,7 @@
         <v>72</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>263</v>
@@ -3520,13 +3520,13 @@
         <v>73</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>259</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>232</v>
@@ -3542,7 +3542,7 @@
         <v>74</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>262</v>
@@ -3562,7 +3562,7 @@
         <v>75</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>265</v>
@@ -3582,13 +3582,13 @@
         <v>76</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>248</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>295</v>
+        <v>508</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>232</v>
@@ -3604,7 +3604,7 @@
         <v>77</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>257</v>
@@ -3624,13 +3624,13 @@
         <v>78</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>253</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>295</v>
+        <v>508</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>232</v>
@@ -3646,13 +3646,13 @@
         <v>79</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>264</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>232</v>
@@ -3668,13 +3668,13 @@
         <v>80</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>268</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>232</v>
@@ -3690,7 +3690,7 @@
         <v>81</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>246</v>
@@ -3710,13 +3710,13 @@
         <v>82</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>252</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>295</v>
+        <v>508</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>232</v>
@@ -3732,13 +3732,13 @@
         <v>83</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>252</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>295</v>
+        <v>508</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>232</v>
@@ -3754,7 +3754,7 @@
         <v>84</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>265</v>
@@ -3774,13 +3774,13 @@
         <v>85</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>251</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>375</v>
+        <v>510</v>
       </c>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
@@ -3794,7 +3794,7 @@
         <v>86</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>247</v>
@@ -3814,7 +3814,7 @@
         <v>87</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>246</v>
@@ -3834,7 +3834,7 @@
         <v>88</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>246</v>
@@ -3854,7 +3854,7 @@
         <v>89</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>263</v>
@@ -3874,7 +3874,7 @@
         <v>90</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>254</v>
@@ -3894,7 +3894,7 @@
         <v>91</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>254</v>
@@ -3914,13 +3914,13 @@
         <v>92</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>248</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>295</v>
+        <v>508</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>232</v>
@@ -3936,7 +3936,7 @@
         <v>93</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>247</v>
@@ -3956,13 +3956,13 @@
         <v>94</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>249</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>295</v>
+        <v>508</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>232</v>
@@ -3978,7 +3978,7 @@
         <v>95</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>247</v>
@@ -3998,7 +3998,7 @@
         <v>96</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>246</v>
@@ -4018,7 +4018,7 @@
         <v>97</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>267</v>
@@ -4038,7 +4038,7 @@
         <v>98</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>261</v>
@@ -4058,7 +4058,7 @@
         <v>99</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>257</v>
@@ -4078,7 +4078,7 @@
         <v>100</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>262</v>
@@ -4098,7 +4098,7 @@
         <v>101</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>246</v>
@@ -4118,7 +4118,7 @@
         <v>102</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>252</v>
@@ -4138,13 +4138,13 @@
         <v>103</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>268</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>232</v>
@@ -4160,7 +4160,7 @@
         <v>104</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>253</v>
@@ -4180,13 +4180,13 @@
         <v>105</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>248</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>295</v>
+        <v>508</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>232</v>
@@ -4202,7 +4202,7 @@
         <v>106</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>262</v>
@@ -4222,7 +4222,7 @@
         <v>107</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>246</v>
@@ -4242,13 +4242,13 @@
         <v>108</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>248</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>295</v>
+        <v>508</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>232</v>
@@ -4264,7 +4264,7 @@
         <v>109</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>253</v>
@@ -4286,13 +4286,13 @@
         <v>110</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>252</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>295</v>
+        <v>508</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>232</v>
@@ -4308,13 +4308,13 @@
         <v>111</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>249</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>295</v>
+        <v>508</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>232</v>
@@ -4330,7 +4330,7 @@
         <v>112</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>247</v>
@@ -4350,7 +4350,7 @@
         <v>113</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>246</v>
@@ -4370,13 +4370,13 @@
         <v>114</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>251</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>375</v>
+        <v>510</v>
       </c>
       <c r="E112" s="1"/>
       <c r="F112" s="1"/>
@@ -4390,13 +4390,13 @@
         <v>115</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>251</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>375</v>
+        <v>510</v>
       </c>
       <c r="E113" s="1"/>
       <c r="F113" s="1"/>
@@ -4410,7 +4410,7 @@
         <v>116</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>254</v>
@@ -4430,13 +4430,13 @@
         <v>117</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>259</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>232</v>
@@ -4452,7 +4452,7 @@
         <v>118</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>269</v>
@@ -4472,7 +4472,7 @@
         <v>119</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>261</v>
@@ -4492,7 +4492,7 @@
         <v>120</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>258</v>
@@ -4512,7 +4512,7 @@
         <v>121</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>260</v>
@@ -4532,7 +4532,7 @@
         <v>122</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>269</v>
@@ -4552,13 +4552,13 @@
         <v>123</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>255</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>232</v>
@@ -4574,7 +4574,7 @@
         <v>124</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>265</v>
@@ -4594,13 +4594,13 @@
         <v>125</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>270</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>232</v>
@@ -4616,7 +4616,7 @@
         <v>126</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>270</v>
@@ -4636,7 +4636,7 @@
         <v>127</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>265</v>
@@ -4656,13 +4656,13 @@
         <v>128</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>256</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>232</v>
@@ -4678,7 +4678,7 @@
         <v>129</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>254</v>
@@ -4698,13 +4698,13 @@
         <v>130</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>251</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>375</v>
+        <v>510</v>
       </c>
       <c r="E128" s="1"/>
       <c r="F128" s="1"/>
@@ -4718,13 +4718,13 @@
         <v>131</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>250</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>291</v>
+        <v>507</v>
       </c>
       <c r="E129" s="1"/>
       <c r="F129" s="1"/>
@@ -4738,7 +4738,7 @@
         <v>132</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>271</v>
@@ -4758,13 +4758,13 @@
         <v>133</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>251</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>375</v>
+        <v>510</v>
       </c>
       <c r="E131" s="1"/>
       <c r="F131" s="1"/>
@@ -4778,13 +4778,13 @@
         <v>134</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>253</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>295</v>
+        <v>508</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>232</v>
@@ -4800,7 +4800,7 @@
         <v>135</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>254</v>
@@ -4820,7 +4820,7 @@
         <v>136</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>265</v>
@@ -4840,13 +4840,13 @@
         <v>137</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>252</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>232</v>
@@ -4862,7 +4862,7 @@
         <v>138</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>247</v>
@@ -4882,13 +4882,13 @@
         <v>139</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>264</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>232</v>
@@ -4904,7 +4904,7 @@
         <v>140</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>257</v>
@@ -4924,13 +4924,13 @@
         <v>141</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>268</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>232</v>
@@ -4946,7 +4946,7 @@
         <v>142</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>247</v>
@@ -4966,7 +4966,7 @@
         <v>143</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>261</v>
@@ -4986,7 +4986,7 @@
         <v>144</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>257</v>
@@ -5006,7 +5006,7 @@
         <v>145</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="C143" s="1">
         <v>0</v>
@@ -5026,13 +5026,13 @@
         <v>146</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>249</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>295</v>
+        <v>508</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>232</v>
@@ -5048,7 +5048,7 @@
         <v>147</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>257</v>
@@ -5068,7 +5068,7 @@
         <v>148</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>257</v>
@@ -5088,7 +5088,7 @@
         <v>149</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>257</v>
@@ -5108,7 +5108,7 @@
         <v>150</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>255</v>
@@ -5128,13 +5128,13 @@
         <v>151</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>255</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>232</v>
@@ -5150,7 +5150,7 @@
         <v>152</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>261</v>
@@ -5170,13 +5170,13 @@
         <v>153</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>264</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>232</v>
@@ -5192,7 +5192,7 @@
         <v>154</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>254</v>
@@ -5214,13 +5214,13 @@
         <v>155</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>251</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>375</v>
+        <v>510</v>
       </c>
       <c r="E153" s="1"/>
       <c r="F153" s="1"/>
@@ -5234,13 +5234,13 @@
         <v>156</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>251</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>375</v>
+        <v>510</v>
       </c>
       <c r="E154" s="1"/>
       <c r="F154" s="1"/>
@@ -5254,13 +5254,13 @@
         <v>157</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>259</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>232</v>
@@ -5276,13 +5276,13 @@
         <v>158</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>264</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>232</v>
@@ -5298,7 +5298,7 @@
         <v>159</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>269</v>
@@ -5318,7 +5318,7 @@
         <v>160</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>254</v>
@@ -5340,13 +5340,13 @@
         <v>161</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>259</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>232</v>
@@ -5362,13 +5362,13 @@
         <v>162</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>251</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>232</v>
@@ -5384,13 +5384,13 @@
         <v>163</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>256</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>232</v>
@@ -5406,7 +5406,7 @@
         <v>164</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>262</v>
@@ -5426,7 +5426,7 @@
         <v>165</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>265</v>
@@ -5446,7 +5446,7 @@
         <v>166</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>268</v>
@@ -5468,7 +5468,7 @@
         <v>167</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>254</v>
@@ -5488,7 +5488,7 @@
         <v>168</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>247</v>
@@ -5508,7 +5508,7 @@
         <v>169</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>268</v>
@@ -5528,7 +5528,7 @@
         <v>170</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>254</v>
@@ -5548,7 +5548,7 @@
         <v>171</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>265</v>
@@ -5568,7 +5568,7 @@
         <v>172</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>247</v>
@@ -5588,7 +5588,7 @@
         <v>173</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>252</v>
@@ -5610,13 +5610,13 @@
         <v>174</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>251</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>375</v>
+        <v>510</v>
       </c>
       <c r="E172" s="1"/>
       <c r="F172" s="1"/>
@@ -5630,7 +5630,7 @@
         <v>175</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>247</v>
@@ -5650,13 +5650,13 @@
         <v>176</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>272</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>291</v>
+        <v>507</v>
       </c>
       <c r="E174" s="1"/>
       <c r="F174" s="1"/>
@@ -5670,7 +5670,7 @@
         <v>177</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>257</v>
@@ -5690,7 +5690,7 @@
         <v>178</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>257</v>
@@ -5710,13 +5710,13 @@
         <v>179</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>255</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>232</v>
@@ -5732,7 +5732,7 @@
         <v>180</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>259</v>
@@ -5752,13 +5752,13 @@
         <v>181</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>255</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>232</v>
@@ -5774,13 +5774,13 @@
         <v>182</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>264</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>232</v>
@@ -5796,13 +5796,13 @@
         <v>183</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>268</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>232</v>
@@ -5818,13 +5818,13 @@
         <v>184</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>251</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>375</v>
+        <v>510</v>
       </c>
       <c r="E182" s="1"/>
       <c r="F182" s="1"/>
@@ -5838,13 +5838,13 @@
         <v>185</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>262</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>375</v>
+        <v>510</v>
       </c>
       <c r="E183" s="1"/>
       <c r="F183" s="1"/>
@@ -5858,7 +5858,7 @@
         <v>186</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>251</v>
@@ -5880,13 +5880,13 @@
         <v>187</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>273</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>291</v>
+        <v>507</v>
       </c>
       <c r="E185" s="1"/>
       <c r="F185" s="1"/>
@@ -5900,7 +5900,7 @@
         <v>188</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>261</v>
@@ -5920,13 +5920,13 @@
         <v>189</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>251</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>232</v>
@@ -5942,13 +5942,13 @@
         <v>190</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>256</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>232</v>
@@ -5964,7 +5964,7 @@
         <v>191</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>274</v>
@@ -5984,7 +5984,7 @@
         <v>192</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>275</v>
@@ -6004,13 +6004,13 @@
         <v>193</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>253</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>295</v>
+        <v>508</v>
       </c>
       <c r="E191" s="1" t="s">
         <v>232</v>
@@ -6026,13 +6026,13 @@
         <v>194</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>256</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>232</v>
@@ -6048,13 +6048,13 @@
         <v>195</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>249</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>295</v>
+        <v>508</v>
       </c>
       <c r="E193" s="1" t="s">
         <v>232</v>
@@ -6070,13 +6070,13 @@
         <v>196</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>266</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>487</v>
+        <v>511</v>
       </c>
       <c r="E194" s="1" t="s">
         <v>232</v>
@@ -6092,7 +6092,7 @@
         <v>197</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>247</v>
@@ -6112,7 +6112,7 @@
         <v>198</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>266</v>
@@ -6134,7 +6134,7 @@
         <v>199</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>247</v>
@@ -6154,7 +6154,7 @@
         <v>200</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>262</v>
@@ -6174,13 +6174,13 @@
         <v>201</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>248</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>295</v>
+        <v>508</v>
       </c>
       <c r="E199" s="1" t="s">
         <v>232</v>
@@ -6196,13 +6196,13 @@
         <v>202</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>264</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E200" s="1" t="s">
         <v>232</v>
@@ -6218,7 +6218,7 @@
         <v>203</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>260</v>
@@ -6238,7 +6238,7 @@
         <v>204</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>247</v>
@@ -6258,13 +6258,13 @@
         <v>205</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>249</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>295</v>
+        <v>508</v>
       </c>
       <c r="E203" s="1" t="s">
         <v>232</v>
@@ -6280,13 +6280,13 @@
         <v>206</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>249</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>295</v>
+        <v>508</v>
       </c>
       <c r="E204" s="1" t="s">
         <v>232</v>
@@ -6302,7 +6302,7 @@
         <v>207</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>266</v>
@@ -6324,7 +6324,7 @@
         <v>208</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>262</v>
@@ -6344,13 +6344,13 @@
         <v>209</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>264</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E207" s="1" t="s">
         <v>232</v>
@@ -6366,13 +6366,13 @@
         <v>210</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>266</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E208" s="1" t="s">
         <v>232</v>
@@ -6388,13 +6388,13 @@
         <v>211</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>253</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>295</v>
+        <v>508</v>
       </c>
       <c r="E209" s="1" t="s">
         <v>232</v>
@@ -6410,13 +6410,13 @@
         <v>212</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>250</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>291</v>
+        <v>507</v>
       </c>
       <c r="E210" s="1"/>
       <c r="F210" s="1"/>
@@ -6430,13 +6430,13 @@
         <v>213</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>251</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>375</v>
+        <v>510</v>
       </c>
       <c r="E211" s="1"/>
       <c r="F211" s="1"/>
@@ -6450,7 +6450,7 @@
         <v>214</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>263</v>
@@ -6470,7 +6470,7 @@
         <v>215</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>274</v>
@@ -6490,13 +6490,13 @@
         <v>216</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>256</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E214" s="1" t="s">
         <v>232</v>
@@ -6512,7 +6512,7 @@
         <v>217</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>263</v>
@@ -6532,13 +6532,13 @@
         <v>218</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>268</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E216" s="1" t="s">
         <v>232</v>
@@ -6554,13 +6554,13 @@
         <v>219</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>268</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>299</v>
+        <v>509</v>
       </c>
       <c r="E217" s="1" t="s">
         <v>232</v>
@@ -6576,7 +6576,7 @@
         <v>220</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>246</v>
@@ -6987,7 +6987,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>246</v>
@@ -7029,7 +7029,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>247</v>
@@ -7071,7 +7071,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>248</v>
@@ -7113,7 +7113,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>249</v>
@@ -7155,7 +7155,7 @@
         <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>250</v>
@@ -7197,7 +7197,7 @@
         <v>10</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>251</v>
@@ -7239,7 +7239,7 @@
         <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>252</v>
@@ -7281,7 +7281,7 @@
         <v>12</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>247</v>
@@ -7323,7 +7323,7 @@
         <v>13</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>251</v>
@@ -7365,7 +7365,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>251</v>
@@ -7407,7 +7407,7 @@
         <v>15</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>246</v>
@@ -7449,7 +7449,7 @@
         <v>16</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>253</v>
@@ -7491,7 +7491,7 @@
         <v>17</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>251</v>
@@ -7533,7 +7533,7 @@
         <v>18</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>254</v>
@@ -7575,7 +7575,7 @@
         <v>19</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>255</v>
@@ -7617,7 +7617,7 @@
         <v>20</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>256</v>
@@ -7659,7 +7659,7 @@
         <v>21</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>248</v>
@@ -7751,7 +7751,7 @@
         <v>22</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>255</v>
@@ -7829,7 +7829,7 @@
         <v>23</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>248</v>
@@ -7917,7 +7917,7 @@
         <v>24</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>257</v>
@@ -7959,7 +7959,7 @@
         <v>25</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>254</v>
@@ -8001,7 +8001,7 @@
         <v>26</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>252</v>
@@ -8043,7 +8043,7 @@
         <v>27</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>249</v>
@@ -8127,7 +8127,7 @@
         <v>28</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>254</v>
@@ -8169,7 +8169,7 @@
         <v>29</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>246</v>
@@ -8211,7 +8211,7 @@
         <v>30</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>254</v>
@@ -8253,7 +8253,7 @@
         <v>31</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>248</v>
@@ -8329,7 +8329,7 @@
         <v>32</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>246</v>
@@ -8371,7 +8371,7 @@
         <v>33</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>249</v>
@@ -8449,7 +8449,7 @@
         <v>34</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>246</v>
@@ -8491,7 +8491,7 @@
         <v>35</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>258</v>
@@ -8533,7 +8533,7 @@
         <v>36</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>258</v>
@@ -8575,7 +8575,7 @@
         <v>37</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>255</v>
@@ -8661,7 +8661,7 @@
         <v>38</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>259</v>
@@ -8745,7 +8745,7 @@
         <v>39</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>260</v>
@@ -8787,26 +8787,38 @@
         <v>40</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>252</v>
       </c>
       <c r="D38" s="1">
-        <v>4</v>
-      </c>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
+        <v>13</v>
+      </c>
+      <c r="E38" s="8">
+        <v>46271</v>
+      </c>
+      <c r="F38" s="6">
+        <v>46270</v>
+      </c>
+      <c r="G38" s="8">
+        <v>46271</v>
+      </c>
       <c r="H38" s="6"/>
       <c r="I38" s="10">
         <v>46197</v>
       </c>
-      <c r="J38" s="10"/>
+      <c r="J38" s="8">
+        <v>46274</v>
+      </c>
       <c r="K38" s="6"/>
       <c r="L38" s="6"/>
-      <c r="M38" s="6"/>
-      <c r="N38" s="6"/>
+      <c r="M38" s="8">
+        <v>46274</v>
+      </c>
+      <c r="N38" s="8">
+        <v>46274</v>
+      </c>
       <c r="O38" s="6"/>
       <c r="P38" s="6"/>
       <c r="Q38" s="6"/>
@@ -8815,11 +8827,17 @@
         <v>46193</v>
       </c>
       <c r="T38" s="6"/>
-      <c r="U38" s="6"/>
+      <c r="U38" s="8">
+        <v>46273</v>
+      </c>
       <c r="V38" s="6"/>
       <c r="W38" s="6"/>
-      <c r="X38" s="6"/>
-      <c r="Y38" s="6"/>
+      <c r="X38" s="6">
+        <v>46270</v>
+      </c>
+      <c r="Y38" s="6">
+        <v>46270</v>
+      </c>
       <c r="Z38" s="6"/>
       <c r="AA38" s="9">
         <v>46192</v>
@@ -8837,7 +8855,7 @@
         <v>41</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>254</v>
@@ -8879,7 +8897,7 @@
         <v>42</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>253</v>
@@ -8963,7 +8981,7 @@
         <v>43</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>253</v>
@@ -9047,7 +9065,7 @@
         <v>44</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>246</v>
@@ -9089,7 +9107,7 @@
         <v>45</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>254</v>
@@ -9131,7 +9149,7 @@
         <v>46</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>261</v>
@@ -9173,7 +9191,7 @@
         <v>47</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>258</v>
@@ -9215,7 +9233,7 @@
         <v>48</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>262</v>
@@ -9257,7 +9275,7 @@
         <v>49</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>262</v>
@@ -9299,7 +9317,7 @@
         <v>50</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>247</v>
@@ -9341,7 +9359,7 @@
         <v>51</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>262</v>
@@ -9383,7 +9401,7 @@
         <v>52</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>247</v>
@@ -9425,7 +9443,7 @@
         <v>53</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>261</v>
@@ -9467,7 +9485,7 @@
         <v>54</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>262</v>
@@ -9509,7 +9527,7 @@
         <v>55</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>263</v>
@@ -9551,7 +9569,7 @@
         <v>56</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>251</v>
@@ -9593,7 +9611,7 @@
         <v>57</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>245</v>
@@ -9635,7 +9653,7 @@
         <v>58</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>250</v>
@@ -9677,7 +9695,7 @@
         <v>59</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>264</v>
@@ -9761,7 +9779,7 @@
         <v>60</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>253</v>
@@ -9845,7 +9863,7 @@
         <v>61</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>253</v>
@@ -9887,7 +9905,7 @@
         <v>62</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>252</v>
@@ -9957,7 +9975,7 @@
         <v>63</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>257</v>
@@ -9999,7 +10017,7 @@
         <v>64</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>254</v>
@@ -10041,7 +10059,7 @@
         <v>65</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>256</v>
@@ -10111,7 +10129,7 @@
         <v>66</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>249</v>
@@ -10177,7 +10195,7 @@
         <v>67</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>257</v>
@@ -10219,7 +10237,7 @@
         <v>68</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>246</v>
@@ -10261,7 +10279,7 @@
         <v>69</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>247</v>
@@ -10303,7 +10321,7 @@
         <v>70</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>263</v>
@@ -10345,7 +10363,7 @@
         <v>71</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>257</v>
@@ -10387,7 +10405,7 @@
         <v>72</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>263</v>
@@ -10429,7 +10447,7 @@
         <v>73</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>259</v>
@@ -10513,7 +10531,7 @@
         <v>74</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>262</v>
@@ -10555,7 +10573,7 @@
         <v>75</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>265</v>
@@ -10597,7 +10615,7 @@
         <v>76</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>248</v>
@@ -10689,7 +10707,7 @@
         <v>77</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>257</v>
@@ -10731,7 +10749,7 @@
         <v>78</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>253</v>
@@ -10815,7 +10833,7 @@
         <v>79</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>264</v>
@@ -10899,7 +10917,7 @@
         <v>80</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>268</v>
@@ -10983,7 +11001,7 @@
         <v>81</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>246</v>
@@ -11025,7 +11043,7 @@
         <v>82</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>252</v>
@@ -11095,7 +11113,7 @@
         <v>83</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>252</v>
@@ -11165,7 +11183,7 @@
         <v>84</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>265</v>
@@ -11207,7 +11225,7 @@
         <v>85</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>251</v>
@@ -11249,7 +11267,7 @@
         <v>86</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>247</v>
@@ -11291,7 +11309,7 @@
         <v>87</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>246</v>
@@ -11333,7 +11351,7 @@
         <v>88</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>246</v>
@@ -11375,7 +11393,7 @@
         <v>89</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>263</v>
@@ -11417,7 +11435,7 @@
         <v>90</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>254</v>
@@ -11459,7 +11477,7 @@
         <v>91</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>254</v>
@@ -11501,7 +11519,7 @@
         <v>92</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>248</v>
@@ -11593,7 +11611,7 @@
         <v>93</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>247</v>
@@ -11635,7 +11653,7 @@
         <v>94</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>249</v>
@@ -11699,7 +11717,7 @@
         <v>95</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>247</v>
@@ -11741,7 +11759,7 @@
         <v>96</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>246</v>
@@ -11783,7 +11801,7 @@
         <v>97</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>267</v>
@@ -11825,7 +11843,7 @@
         <v>98</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>261</v>
@@ -11867,7 +11885,7 @@
         <v>99</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>257</v>
@@ -11909,7 +11927,7 @@
         <v>100</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>262</v>
@@ -11951,7 +11969,7 @@
         <v>101</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>246</v>
@@ -11993,7 +12011,7 @@
         <v>102</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>252</v>
@@ -12063,7 +12081,7 @@
         <v>103</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>268</v>
@@ -12139,7 +12157,7 @@
         <v>104</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>253</v>
@@ -12181,7 +12199,7 @@
         <v>105</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>248</v>
@@ -12273,7 +12291,7 @@
         <v>106</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>262</v>
@@ -12315,7 +12333,7 @@
         <v>107</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>246</v>
@@ -12357,7 +12375,7 @@
         <v>108</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>248</v>
@@ -12441,7 +12459,7 @@
         <v>109</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>253</v>
@@ -12483,7 +12501,7 @@
         <v>110</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>252</v>
@@ -12533,7 +12551,7 @@
         <v>111</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>249</v>
@@ -12617,7 +12635,7 @@
         <v>112</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>247</v>
@@ -12659,7 +12677,7 @@
         <v>113</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>246</v>
@@ -12701,7 +12719,7 @@
         <v>114</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>251</v>
@@ -12743,7 +12761,7 @@
         <v>115</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>251</v>
@@ -12785,7 +12803,7 @@
         <v>116</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>254</v>
@@ -12827,7 +12845,7 @@
         <v>117</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>259</v>
@@ -12911,7 +12929,7 @@
         <v>118</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>269</v>
@@ -12953,7 +12971,7 @@
         <v>119</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>261</v>
@@ -12995,7 +13013,7 @@
         <v>120</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>258</v>
@@ -13037,7 +13055,7 @@
         <v>121</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>260</v>
@@ -13079,7 +13097,7 @@
         <v>122</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>269</v>
@@ -13121,7 +13139,7 @@
         <v>123</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>255</v>
@@ -13199,7 +13217,7 @@
         <v>124</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>265</v>
@@ -13241,7 +13259,7 @@
         <v>125</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>270</v>
@@ -13283,7 +13301,7 @@
         <v>126</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>270</v>
@@ -13325,7 +13343,7 @@
         <v>127</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>265</v>
@@ -13367,7 +13385,7 @@
         <v>128</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>256</v>
@@ -13447,7 +13465,7 @@
         <v>129</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>254</v>
@@ -13489,7 +13507,7 @@
         <v>130</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>251</v>
@@ -13531,7 +13549,7 @@
         <v>131</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>250</v>
@@ -13573,7 +13591,7 @@
         <v>132</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>271</v>
@@ -13615,7 +13633,7 @@
         <v>133</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>251</v>
@@ -13657,7 +13675,7 @@
         <v>134</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>253</v>
@@ -13741,7 +13759,7 @@
         <v>135</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>254</v>
@@ -13783,7 +13801,7 @@
         <v>136</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>265</v>
@@ -13825,7 +13843,7 @@
         <v>137</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>252</v>
@@ -13895,7 +13913,7 @@
         <v>138</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>247</v>
@@ -13937,7 +13955,7 @@
         <v>139</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>264</v>
@@ -14015,7 +14033,7 @@
         <v>140</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>257</v>
@@ -14057,7 +14075,7 @@
         <v>141</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>268</v>
@@ -14141,7 +14159,7 @@
         <v>142</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>247</v>
@@ -14183,7 +14201,7 @@
         <v>143</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>261</v>
@@ -14225,7 +14243,7 @@
         <v>144</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>257</v>
@@ -14267,7 +14285,7 @@
         <v>145</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="C143" s="1">
         <v>0</v>
@@ -14309,7 +14327,7 @@
         <v>146</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>249</v>
@@ -14393,7 +14411,7 @@
         <v>147</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>257</v>
@@ -14435,7 +14453,7 @@
         <v>148</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>257</v>
@@ -14477,7 +14495,7 @@
         <v>149</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>257</v>
@@ -14519,7 +14537,7 @@
         <v>150</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>255</v>
@@ -14561,7 +14579,7 @@
         <v>151</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>255</v>
@@ -14645,7 +14663,7 @@
         <v>152</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>261</v>
@@ -14687,7 +14705,7 @@
         <v>153</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>264</v>
@@ -14755,7 +14773,7 @@
         <v>154</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>254</v>
@@ -14797,7 +14815,7 @@
         <v>155</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>251</v>
@@ -14839,7 +14857,7 @@
         <v>156</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>251</v>
@@ -14881,13 +14899,13 @@
         <v>157</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>259</v>
       </c>
       <c r="D155" s="1">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E155" s="8">
         <v>46154</v>
@@ -14896,8 +14914,12 @@
       <c r="G155" s="8">
         <v>46154</v>
       </c>
-      <c r="H155" s="6"/>
-      <c r="I155" s="6"/>
+      <c r="H155" s="6">
+        <v>46286</v>
+      </c>
+      <c r="I155" s="6">
+        <v>46286</v>
+      </c>
       <c r="J155" s="8">
         <v>46154</v>
       </c>
@@ -14945,7 +14967,7 @@
         <v>158</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>264</v>
@@ -14987,7 +15009,7 @@
         <v>159</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>269</v>
@@ -15029,7 +15051,7 @@
         <v>160</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>254</v>
@@ -15071,7 +15093,7 @@
         <v>161</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>259</v>
@@ -15153,7 +15175,7 @@
         <v>162</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>251</v>
@@ -15195,7 +15217,7 @@
         <v>163</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>256</v>
@@ -15275,7 +15297,7 @@
         <v>164</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>262</v>
@@ -15317,7 +15339,7 @@
         <v>165</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>265</v>
@@ -15359,7 +15381,7 @@
         <v>166</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>268</v>
@@ -15401,7 +15423,7 @@
         <v>167</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>254</v>
@@ -15443,7 +15465,7 @@
         <v>168</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>247</v>
@@ -15485,7 +15507,7 @@
         <v>169</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>268</v>
@@ -15527,7 +15549,7 @@
         <v>170</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>254</v>
@@ -15569,7 +15591,7 @@
         <v>171</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>265</v>
@@ -15611,7 +15633,7 @@
         <v>172</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>247</v>
@@ -15653,7 +15675,7 @@
         <v>173</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>252</v>
@@ -15695,7 +15717,7 @@
         <v>174</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>251</v>
@@ -15737,7 +15759,7 @@
         <v>175</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>247</v>
@@ -15779,7 +15801,7 @@
         <v>176</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>272</v>
@@ -15821,7 +15843,7 @@
         <v>177</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>257</v>
@@ -15863,7 +15885,7 @@
         <v>178</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>257</v>
@@ -15905,7 +15927,7 @@
         <v>179</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>255</v>
@@ -15991,7 +16013,7 @@
         <v>180</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>259</v>
@@ -16033,7 +16055,7 @@
         <v>181</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>255</v>
@@ -16103,7 +16125,7 @@
         <v>182</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>264</v>
@@ -16181,7 +16203,7 @@
         <v>183</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>268</v>
@@ -16253,7 +16275,7 @@
         <v>184</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>251</v>
@@ -16295,7 +16317,7 @@
         <v>185</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>262</v>
@@ -16337,7 +16359,7 @@
         <v>186</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>251</v>
@@ -16379,7 +16401,7 @@
         <v>187</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>273</v>
@@ -16421,7 +16443,7 @@
         <v>188</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>261</v>
@@ -16463,7 +16485,7 @@
         <v>189</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>251</v>
@@ -16505,7 +16527,7 @@
         <v>190</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>256</v>
@@ -16585,7 +16607,7 @@
         <v>191</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>274</v>
@@ -16627,7 +16649,7 @@
         <v>192</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>275</v>
@@ -16669,7 +16691,7 @@
         <v>193</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>253</v>
@@ -16753,13 +16775,13 @@
         <v>194</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>256</v>
       </c>
       <c r="D192" s="1">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E192" s="6">
         <v>46149</v>
@@ -16770,8 +16792,12 @@
       <c r="G192" s="6">
         <v>46152</v>
       </c>
-      <c r="H192" s="6"/>
-      <c r="I192" s="6"/>
+      <c r="H192" s="6">
+        <v>46286</v>
+      </c>
+      <c r="I192" s="6">
+        <v>46286</v>
+      </c>
       <c r="J192" s="6">
         <v>46152</v>
       </c>
@@ -16781,7 +16807,9 @@
       <c r="L192" s="8">
         <v>46177</v>
       </c>
-      <c r="M192" s="6"/>
+      <c r="M192" s="8">
+        <v>46286</v>
+      </c>
       <c r="N192" s="8">
         <v>46177</v>
       </c>
@@ -16833,7 +16861,7 @@
         <v>195</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>249</v>
@@ -16905,7 +16933,7 @@
         <v>196</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>266</v>
@@ -16947,7 +16975,7 @@
         <v>197</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>247</v>
@@ -16989,7 +17017,7 @@
         <v>198</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>266</v>
@@ -17031,7 +17059,7 @@
         <v>199</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>247</v>
@@ -17073,7 +17101,7 @@
         <v>200</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>262</v>
@@ -17115,7 +17143,7 @@
         <v>201</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>248</v>
@@ -17207,7 +17235,7 @@
         <v>202</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>264</v>
@@ -17291,7 +17319,7 @@
         <v>203</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>260</v>
@@ -17333,7 +17361,7 @@
         <v>204</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>247</v>
@@ -17375,7 +17403,7 @@
         <v>205</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>249</v>
@@ -17459,7 +17487,7 @@
         <v>206</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>249</v>
@@ -17537,7 +17565,7 @@
         <v>207</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>266</v>
@@ -17579,7 +17607,7 @@
         <v>208</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>262</v>
@@ -17621,7 +17649,7 @@
         <v>209</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>264</v>
@@ -17679,7 +17707,7 @@
         <v>210</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>266</v>
@@ -17749,7 +17777,7 @@
         <v>211</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>253</v>
@@ -17833,7 +17861,7 @@
         <v>212</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>250</v>
@@ -17875,7 +17903,7 @@
         <v>213</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>251</v>
@@ -17917,7 +17945,7 @@
         <v>214</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>263</v>
@@ -17959,7 +17987,7 @@
         <v>215</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>274</v>
@@ -18001,7 +18029,7 @@
         <v>216</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>256</v>
@@ -18079,7 +18107,7 @@
         <v>217</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>263</v>
@@ -18121,7 +18149,7 @@
         <v>218</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>268</v>
@@ -18205,7 +18233,7 @@
         <v>219</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>268</v>
@@ -18289,7 +18317,7 @@
         <v>220</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>246</v>

--- a/Matar Trainings.xlsx
+++ b/Matar Trainings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l.karuru\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72F4B6E8-5257-4DA6-B5C5-344DFDF46082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CD39485-1A96-4935-9C1E-FBE5787DA781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{2ACD8935-9A55-49F4-8AD3-9F8021E2249D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2ACD8935-9A55-49F4-8AD3-9F8021E2249D}"/>
   </bookViews>
   <sheets>
     <sheet name="Meta Data" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1658" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1665" uniqueCount="513">
   <si>
     <t>Emp. No.</t>
   </si>
@@ -1240,331 +1240,334 @@
     <t>Mark Merill Jovenes Tirol</t>
   </si>
   <si>
+    <t>Francis Agbor Eyong Atem</t>
+  </si>
+  <si>
+    <t>Siraj Moolakkappil</t>
+  </si>
+  <si>
+    <t>Mohamed Bilal Muneer Basha</t>
+  </si>
+  <si>
+    <t>Alen Cherippanat Babu</t>
+  </si>
+  <si>
+    <t>Mohamed Shafras Jawlangull</t>
+  </si>
+  <si>
+    <t>Renson Gicheha Gicheru</t>
+  </si>
+  <si>
+    <t>Mohamed Faris Mohamed Naleem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shihabdeen Seeni Mohamed </t>
+  </si>
+  <si>
+    <t>Prakyath Prabhakar Amin</t>
+  </si>
+  <si>
+    <t>Julius Kateregga</t>
+  </si>
+  <si>
+    <t>Kishanraj Pulenthiran</t>
+  </si>
+  <si>
+    <t>James Kariungi Muthee</t>
+  </si>
+  <si>
+    <t>Kasansula Francis Kiwanuka</t>
+  </si>
+  <si>
+    <t>Arnel Neri Montemayor</t>
+  </si>
+  <si>
+    <t>Erick Omondi Okoyo</t>
+  </si>
+  <si>
+    <t>Trevin Christopher Neydorf</t>
+  </si>
+  <si>
+    <t>Mohamed Mufaris Mohamed Jameel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jasim Kinarullaparambath Kunhabdulla </t>
+  </si>
+  <si>
+    <t>Naser Qasim Mohammad Alhaj Ahmed</t>
+  </si>
+  <si>
+    <t>Jeffrey Sayson Bagatua</t>
+  </si>
+  <si>
+    <t>Wali Mohammed Sabry</t>
+  </si>
+  <si>
+    <t>Rommel Tamayo Eleosida</t>
+  </si>
+  <si>
+    <t>Errolnil Purificacion Atienza</t>
+  </si>
+  <si>
+    <t>Hernan John Baguion Murcillos</t>
+  </si>
+  <si>
+    <t>Ivan Raphael Macatangay Del Mundo</t>
+  </si>
+  <si>
+    <t>Jerico Tallorin Atienzo</t>
+  </si>
+  <si>
+    <t>Alvin Tumboc Cuevas</t>
+  </si>
+  <si>
+    <t>James Andrew Aquino Rodillo</t>
+  </si>
+  <si>
+    <t>Alvin Cataquiz Austria</t>
+  </si>
+  <si>
+    <t>Jayson Ruz Oligan</t>
+  </si>
+  <si>
+    <t>John Michael Angelo Mesina Clemen</t>
+  </si>
+  <si>
+    <t>Lemuel Carcellar Macatangay</t>
+  </si>
+  <si>
+    <t>Nikko Villanueva Cruz</t>
+  </si>
+  <si>
+    <t>Justin Paolo Macatangay Ilao</t>
+  </si>
+  <si>
+    <t>Jake Alinabon Salibay</t>
+  </si>
+  <si>
+    <t>Marlon Yuson Pamplona</t>
+  </si>
+  <si>
+    <t>Joe Vergil Jr Calanza Dormitorio</t>
+  </si>
+  <si>
+    <t>Bonifacio Arano Bayer</t>
+  </si>
+  <si>
+    <t>Sumedha Pradeep Dissanayaka</t>
+  </si>
+  <si>
+    <t>Yuvashanth Somasuntharam kukasuthan</t>
+  </si>
+  <si>
+    <t>Jonel Catibog Katigbak</t>
+  </si>
+  <si>
+    <t>Catalino Mendoza Rojas</t>
+  </si>
+  <si>
+    <t>Murshidul Haq Patteri Thazhe Kuni</t>
+  </si>
+  <si>
+    <t>Nisham Kizhakke Valappil</t>
+  </si>
+  <si>
+    <t>Pasidu Pamodaya Rathnayake Rathnayake Mudiyanselage</t>
+  </si>
+  <si>
+    <t>Chalana Ishan Dishanayake Dishanayake Pathiranage</t>
+  </si>
+  <si>
+    <t>Mohamed Ahthir Abdul Majeed</t>
+  </si>
+  <si>
+    <t>Niroshan Abesingha Abesingha Karunarathna Mudalige</t>
+  </si>
+  <si>
+    <t>Sathis Gunawardhana Dikella Kandha Yakdhehirallage</t>
+  </si>
+  <si>
+    <t>Tharaka Thanujaya Dissanayaka Dissanayaka Mudiyanselage</t>
+  </si>
+  <si>
+    <t>Nishan Ekanayake Ekanayake Mudiyanselage</t>
+  </si>
+  <si>
+    <t>Jacky Chan Nava Gastardo</t>
+  </si>
+  <si>
+    <t>Mohammed Fahim Mohammed Laffir</t>
+  </si>
+  <si>
+    <t>Sameera Lakmal Rupasinghe Arachchige</t>
+  </si>
+  <si>
+    <t>Dushan Priyankara Herath Herath Mudiyanselage</t>
+  </si>
+  <si>
+    <t>Pathmapriyan Muruguppilla</t>
+  </si>
+  <si>
+    <t>Roshan Chaminda Udawaththa Udawaththa Kankanamge</t>
+  </si>
+  <si>
+    <t>Kusal Sharmila Hewa Kokawalage</t>
+  </si>
+  <si>
+    <t>Mohomed Minnas Mohomed Ramees</t>
+  </si>
+  <si>
+    <t>Mabin Pauly</t>
+  </si>
+  <si>
+    <t>Jahsim Saycon Apila</t>
+  </si>
+  <si>
+    <t>Shern Sebastian Sebastian Simon</t>
+  </si>
+  <si>
+    <t>Wai Hin Phyo</t>
+  </si>
+  <si>
+    <t>Hicham Charkaoui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mohamed Shaheer Mohamed Laffir </t>
+  </si>
+  <si>
+    <t>Antony Kamau Kageche</t>
+  </si>
+  <si>
+    <t>Abdulrashid Byarugaba </t>
+  </si>
+  <si>
+    <t>Justine Tiangson Clave</t>
+  </si>
+  <si>
+    <t>Harikaran Seenithamby</t>
+  </si>
+  <si>
+    <t>Wycliffe Mushori</t>
+  </si>
+  <si>
+    <t>Peter Nganga Kamau</t>
+  </si>
+  <si>
+    <t>Sumesh Soman</t>
+  </si>
+  <si>
+    <t>Muhammed Ashiq Mohamed Mumtaz</t>
+  </si>
+  <si>
+    <t>Arvin Clyde D.Crisme</t>
+  </si>
+  <si>
+    <t>Gary John Packer</t>
+  </si>
+  <si>
+    <t>Ifras Mohammed</t>
+  </si>
+  <si>
+    <t>Alby Manchandiyil Antony</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ifran Ansari </t>
+  </si>
+  <si>
+    <t>Piratheepan Thiyagarasa</t>
+  </si>
+  <si>
+    <t>Moustafa Hassan Ibrahim Elsayyad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harsha Shetty </t>
+  </si>
+  <si>
+    <t>Kevin Carl Enriquez Serrano</t>
+  </si>
+  <si>
+    <t>Romie Ross Tamayo Eleosida</t>
+  </si>
+  <si>
+    <t>Quennan Carandang Cuesta</t>
+  </si>
+  <si>
+    <t>Lester John Fuentes Monter</t>
+  </si>
+  <si>
+    <t>Neil Jhon Sabile Ramos</t>
+  </si>
+  <si>
+    <t>Kim Harvey Cuevas Ayag</t>
+  </si>
+  <si>
+    <t>Nelson Jr Ybut Sancho</t>
+  </si>
+  <si>
+    <t>Rolly Miano Valdez</t>
+  </si>
+  <si>
+    <t>Daniel Bacolcol Orquiza</t>
+  </si>
+  <si>
+    <t>Roby Chua Malinao</t>
+  </si>
+  <si>
+    <t>Lorence Cardenas Cabales</t>
+  </si>
+  <si>
+    <t>Emmanuel Richard Marasigan Velasco</t>
+  </si>
+  <si>
+    <t>Michael Jorge Toscano Masaoy</t>
+  </si>
+  <si>
+    <t>Jeffrey De Vera Cabico</t>
+  </si>
+  <si>
+    <t>Joe Peter Angustia Pimentel</t>
+  </si>
+  <si>
+    <t>Mark Roentgen Macatangay Delen</t>
+  </si>
+  <si>
+    <t>Arjay Imperial Gabarda</t>
+  </si>
+  <si>
+    <t>Noey Francisco Canonizado</t>
+  </si>
+  <si>
+    <t>Omar Zaki Saad Abdel Nabi</t>
+  </si>
+  <si>
+    <t>Abdul Rehman Mohammed Abdul Mohammed</t>
+  </si>
+  <si>
+    <t>Christian Merck Morada Martija</t>
+  </si>
+  <si>
+    <t>Imesha Rashmi Mudannayaka Mudannayakage</t>
+  </si>
+  <si>
+    <t>Sajith Dulanjana Kumara Rathnayaka Mudiyanselage</t>
+  </si>
+  <si>
+    <t>Thisura Kaumal Wijesinghe</t>
+  </si>
+  <si>
+    <t>Shanel Rukshan Perera Kurana Patabendige</t>
+  </si>
+  <si>
+    <t>Abeykoon Mudiyanselage Sasitha Dinushka Abeykoon</t>
+  </si>
+  <si>
+    <t>Jerusha Anns Philip</t>
+  </si>
+  <si>
     <t>Kennedy Gichuhi Ngaruiya</t>
   </si>
   <si>
-    <t>Francis Agbor Eyong Atem</t>
-  </si>
-  <si>
-    <t>Siraj Moolakkappil</t>
-  </si>
-  <si>
-    <t>Mohamed Bilal Muneer Basha</t>
-  </si>
-  <si>
-    <t>Alen Cherippanat Babu</t>
-  </si>
-  <si>
-    <t>Mohamed Shafras Jawlangull</t>
-  </si>
-  <si>
-    <t>Renson Gicheha Gicheru</t>
-  </si>
-  <si>
-    <t>Mohamed Faris Mohamed Naleem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shihabdeen Seeni Mohamed </t>
-  </si>
-  <si>
-    <t>Prakyath Prabhakar Amin</t>
-  </si>
-  <si>
-    <t>Julius Kateregga</t>
-  </si>
-  <si>
-    <t>Kishanraj Pulenthiran</t>
-  </si>
-  <si>
-    <t>James Kariungi Muthee</t>
-  </si>
-  <si>
-    <t>Kasansula Francis Kiwanuka</t>
-  </si>
-  <si>
-    <t>Arnel Neri Montemayor</t>
-  </si>
-  <si>
-    <t>Erick Omondi Okoyo</t>
-  </si>
-  <si>
-    <t>Trevin Christopher Neydorf</t>
-  </si>
-  <si>
-    <t>Mohamed Mufaris Mohamed Jameel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jasim Kinarullaparambath Kunhabdulla </t>
-  </si>
-  <si>
-    <t>Naser Qasim Mohammad Alhaj Ahmed</t>
-  </si>
-  <si>
-    <t>Jeffrey Sayson Bagatua</t>
-  </si>
-  <si>
-    <t>Wali Mohammed Sabry</t>
-  </si>
-  <si>
-    <t>Rommel Tamayo Eleosida</t>
-  </si>
-  <si>
-    <t>Errolnil Purificacion Atienza</t>
-  </si>
-  <si>
-    <t>Hernan John Baguion Murcillos</t>
-  </si>
-  <si>
-    <t>Ivan Raphael Macatangay Del Mundo</t>
-  </si>
-  <si>
-    <t>Jerico Tallorin Atienzo</t>
-  </si>
-  <si>
-    <t>Alvin Tumboc Cuevas</t>
-  </si>
-  <si>
-    <t>James Andrew Aquino Rodillo</t>
-  </si>
-  <si>
-    <t>Alvin Cataquiz Austria</t>
-  </si>
-  <si>
-    <t>Jayson Ruz Oligan</t>
-  </si>
-  <si>
-    <t>John Michael Angelo Mesina Clemen</t>
-  </si>
-  <si>
-    <t>Lemuel Carcellar Macatangay</t>
-  </si>
-  <si>
-    <t>Nikko Villanueva Cruz</t>
-  </si>
-  <si>
-    <t>Justin Paolo Macatangay Ilao</t>
-  </si>
-  <si>
-    <t>Jake Alinabon Salibay</t>
-  </si>
-  <si>
-    <t>Marlon Yuson Pamplona</t>
-  </si>
-  <si>
-    <t>Joe Vergil Jr Calanza Dormitorio</t>
-  </si>
-  <si>
-    <t>Bonifacio Arano Bayer</t>
-  </si>
-  <si>
-    <t>Sumedha Pradeep Dissanayaka</t>
-  </si>
-  <si>
-    <t>Yuvashanth Somasuntharam kukasuthan</t>
-  </si>
-  <si>
-    <t>Jonel Catibog Katigbak</t>
-  </si>
-  <si>
-    <t>Catalino Mendoza Rojas</t>
-  </si>
-  <si>
-    <t>Murshidul Haq Patteri Thazhe Kuni</t>
-  </si>
-  <si>
-    <t>Nisham Kizhakke Valappil</t>
-  </si>
-  <si>
-    <t>Pasidu Pamodaya Rathnayake Rathnayake Mudiyanselage</t>
-  </si>
-  <si>
-    <t>Chalana Ishan Dishanayake Dishanayake Pathiranage</t>
-  </si>
-  <si>
-    <t>Mohamed Ahthir Abdul Majeed</t>
-  </si>
-  <si>
-    <t>Niroshan Abesingha Abesingha Karunarathna Mudalige</t>
-  </si>
-  <si>
-    <t>Sathis Gunawardhana Dikella Kandha Yakdhehirallage</t>
-  </si>
-  <si>
-    <t>Tharaka Thanujaya Dissanayaka Dissanayaka Mudiyanselage</t>
-  </si>
-  <si>
-    <t>Nishan Ekanayake Ekanayake Mudiyanselage</t>
-  </si>
-  <si>
-    <t>Jacky Chan Nava Gastardo</t>
-  </si>
-  <si>
-    <t>Mohammed Fahim Mohammed Laffir</t>
-  </si>
-  <si>
-    <t>Sameera Lakmal Rupasinghe Arachchige</t>
-  </si>
-  <si>
-    <t>Dushan Priyankara Herath Herath Mudiyanselage</t>
-  </si>
-  <si>
-    <t>Pathmapriyan Muruguppilla</t>
-  </si>
-  <si>
-    <t>Roshan Chaminda Udawaththa Udawaththa Kankanamge</t>
-  </si>
-  <si>
-    <t>Kusal Sharmila Hewa Kokawalage</t>
-  </si>
-  <si>
-    <t>Mohomed Minnas Mohomed Ramees</t>
-  </si>
-  <si>
-    <t>Mabin Pauly</t>
-  </si>
-  <si>
-    <t>Jahsim Saycon Apila</t>
-  </si>
-  <si>
-    <t>Shern Sebastian Sebastian Simon</t>
-  </si>
-  <si>
-    <t>Wai Hin Phyo</t>
-  </si>
-  <si>
-    <t>Hicham Charkaoui</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mohamed Shaheer Mohamed Laffir </t>
-  </si>
-  <si>
-    <t>Antony Kamau Kageche</t>
-  </si>
-  <si>
-    <t>Abdulrashid Byarugaba </t>
-  </si>
-  <si>
-    <t>Justine Tiangson Clave</t>
-  </si>
-  <si>
-    <t>Harikaran Seenithamby</t>
-  </si>
-  <si>
-    <t>Wycliffe Mushori</t>
-  </si>
-  <si>
-    <t>Peter Nganga Kamau</t>
-  </si>
-  <si>
-    <t>Sumesh Soman</t>
-  </si>
-  <si>
-    <t>Muhammed Ashiq Mohamed Mumtaz</t>
-  </si>
-  <si>
-    <t>Arvin Clyde D.Crisme</t>
-  </si>
-  <si>
-    <t>Gary John Packer</t>
-  </si>
-  <si>
-    <t>Ifras Mohammed</t>
-  </si>
-  <si>
-    <t>Alby Manchandiyil Antony</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ifran Ansari </t>
-  </si>
-  <si>
-    <t>Piratheepan Thiyagarasa</t>
-  </si>
-  <si>
-    <t>Moustafa Hassan Ibrahim Elsayyad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harsha Shetty </t>
-  </si>
-  <si>
-    <t>Kevin Carl Enriquez Serrano</t>
-  </si>
-  <si>
-    <t>Romie Ross Tamayo Eleosida</t>
-  </si>
-  <si>
-    <t>Quennan Carandang Cuesta</t>
-  </si>
-  <si>
-    <t>Lester John Fuentes Monter</t>
-  </si>
-  <si>
-    <t>Neil Jhon Sabile Ramos</t>
-  </si>
-  <si>
-    <t>Kim Harvey Cuevas Ayag</t>
-  </si>
-  <si>
-    <t>Nelson Jr Ybut Sancho</t>
-  </si>
-  <si>
-    <t>Rolly Miano Valdez</t>
-  </si>
-  <si>
-    <t>Daniel Bacolcol Orquiza</t>
-  </si>
-  <si>
-    <t>Roby Chua Malinao</t>
-  </si>
-  <si>
-    <t>Lorence Cardenas Cabales</t>
-  </si>
-  <si>
-    <t>Emmanuel Richard Marasigan Velasco</t>
-  </si>
-  <si>
-    <t>Michael Jorge Toscano Masaoy</t>
-  </si>
-  <si>
-    <t>Jeffrey De Vera Cabico</t>
-  </si>
-  <si>
-    <t>Joe Peter Angustia Pimentel</t>
-  </si>
-  <si>
-    <t>Mark Roentgen Macatangay Delen</t>
-  </si>
-  <si>
-    <t>Arjay Imperial Gabarda</t>
-  </si>
-  <si>
-    <t>Noey Francisco Canonizado</t>
-  </si>
-  <si>
-    <t>Omar Zaki Saad Abdel Nabi</t>
-  </si>
-  <si>
-    <t>Abdul Rehman Mohammed Abdul Mohammed</t>
-  </si>
-  <si>
-    <t>Christian Merck Morada Martija</t>
-  </si>
-  <si>
-    <t>Imesha Rashmi Mudannayaka Mudannayakage</t>
-  </si>
-  <si>
-    <t>Sajith Dulanjana Kumara Rathnayaka Mudiyanselage</t>
-  </si>
-  <si>
-    <t>Thisura Kaumal Wijesinghe</t>
-  </si>
-  <si>
-    <t>Shanel Rukshan Perera Kurana Patabendige</t>
-  </si>
-  <si>
-    <t>Abeykoon Mudiyanselage Sasitha Dinushka Abeykoon</t>
-  </si>
-  <si>
-    <t>Jerusha Anns Philip</t>
+    <t>Justine Angwenyi Momanyi</t>
   </si>
   <si>
     <t>Management</t>
@@ -1590,7 +1593,7 @@
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
     <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yyyy;@"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1618,6 +1621,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1680,7 +1689,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1696,6 +1705,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2090,7 +2102,7 @@
         <v>245</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
@@ -2150,7 +2162,7 @@
         <v>248</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>232</v>
@@ -2172,7 +2184,7 @@
         <v>249</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>232</v>
@@ -2214,7 +2226,7 @@
         <v>251</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>232</v>
@@ -2236,7 +2248,7 @@
         <v>252</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>232</v>
@@ -2278,7 +2290,7 @@
         <v>251</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>232</v>
@@ -2300,7 +2312,7 @@
         <v>251</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
@@ -2337,10 +2349,10 @@
         <v>302</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>232</v>
@@ -2362,7 +2374,7 @@
         <v>251</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>232</v>
@@ -2404,7 +2416,7 @@
         <v>255</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>232</v>
@@ -2426,7 +2438,7 @@
         <v>256</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>232</v>
@@ -2448,7 +2460,7 @@
         <v>248</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>232</v>
@@ -2470,7 +2482,7 @@
         <v>255</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>232</v>
@@ -2492,7 +2504,7 @@
         <v>248</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>232</v>
@@ -2554,7 +2566,7 @@
         <v>252</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>232</v>
@@ -2576,7 +2588,7 @@
         <v>249</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>232</v>
@@ -2658,7 +2670,7 @@
         <v>248</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>232</v>
@@ -2700,7 +2712,7 @@
         <v>249</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>232</v>
@@ -2782,7 +2794,7 @@
         <v>255</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>232</v>
@@ -2804,7 +2816,7 @@
         <v>259</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>232</v>
@@ -2846,7 +2858,7 @@
         <v>252</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>232</v>
@@ -2888,7 +2900,7 @@
         <v>253</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>232</v>
@@ -2910,7 +2922,7 @@
         <v>253</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>232</v>
@@ -3172,7 +3184,7 @@
         <v>251</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>232</v>
@@ -3194,7 +3206,7 @@
         <v>245</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
@@ -3234,7 +3246,7 @@
         <v>264</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>232</v>
@@ -3256,7 +3268,7 @@
         <v>253</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>232</v>
@@ -3275,10 +3287,10 @@
         <v>347</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>232</v>
@@ -3300,7 +3312,7 @@
         <v>252</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>232</v>
@@ -3362,7 +3374,7 @@
         <v>256</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>232</v>
@@ -3384,7 +3396,7 @@
         <v>249</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>232</v>
@@ -3526,7 +3538,7 @@
         <v>259</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>232</v>
@@ -3588,7 +3600,7 @@
         <v>248</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>232</v>
@@ -3630,7 +3642,7 @@
         <v>253</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>232</v>
@@ -3652,7 +3664,7 @@
         <v>264</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>232</v>
@@ -3674,7 +3686,7 @@
         <v>268</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>232</v>
@@ -3716,7 +3728,7 @@
         <v>252</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>232</v>
@@ -3738,7 +3750,7 @@
         <v>252</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>232</v>
@@ -3780,7 +3792,7 @@
         <v>251</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
@@ -3920,7 +3932,7 @@
         <v>248</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>232</v>
@@ -3962,7 +3974,7 @@
         <v>249</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>232</v>
@@ -4144,7 +4156,7 @@
         <v>268</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>232</v>
@@ -4163,7 +4175,7 @@
         <v>390</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>263</v>
@@ -4186,7 +4198,7 @@
         <v>248</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>232</v>
@@ -4248,7 +4260,7 @@
         <v>248</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>232</v>
@@ -4267,7 +4279,7 @@
         <v>395</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>254</v>
@@ -4292,7 +4304,7 @@
         <v>252</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>508</v>
+        <v>254</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>232</v>
@@ -4314,7 +4326,7 @@
         <v>249</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>232</v>
@@ -4329,14 +4341,14 @@
       <c r="A110" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>398</v>
+      <c r="B110" s="1" t="e">
+        <v>#N/A</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="D110" s="1" t="s">
-        <v>254</v>
+      <c r="D110" s="1" t="e">
+        <v>#N/A</v>
       </c>
       <c r="E110" s="1"/>
       <c r="F110" s="1"/>
@@ -4350,7 +4362,7 @@
         <v>113</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>246</v>
@@ -4370,13 +4382,13 @@
         <v>114</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>251</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E112" s="1"/>
       <c r="F112" s="1"/>
@@ -4390,13 +4402,13 @@
         <v>115</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>251</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E113" s="1"/>
       <c r="F113" s="1"/>
@@ -4410,7 +4422,7 @@
         <v>116</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>254</v>
@@ -4430,13 +4442,13 @@
         <v>117</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>259</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>232</v>
@@ -4452,7 +4464,7 @@
         <v>118</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>269</v>
@@ -4472,7 +4484,7 @@
         <v>119</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>261</v>
@@ -4492,7 +4504,7 @@
         <v>120</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>258</v>
@@ -4512,7 +4524,7 @@
         <v>121</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>260</v>
@@ -4532,7 +4544,7 @@
         <v>122</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>269</v>
@@ -4552,13 +4564,13 @@
         <v>123</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>255</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>232</v>
@@ -4574,7 +4586,7 @@
         <v>124</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>265</v>
@@ -4594,13 +4606,13 @@
         <v>125</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>270</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>232</v>
@@ -4616,7 +4628,7 @@
         <v>126</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>270</v>
@@ -4636,7 +4648,7 @@
         <v>127</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>265</v>
@@ -4656,13 +4668,13 @@
         <v>128</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>256</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>232</v>
@@ -4678,7 +4690,7 @@
         <v>129</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>254</v>
@@ -4698,13 +4710,13 @@
         <v>130</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>251</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E128" s="1"/>
       <c r="F128" s="1"/>
@@ -4718,13 +4730,13 @@
         <v>131</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>250</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E129" s="1"/>
       <c r="F129" s="1"/>
@@ -4738,7 +4750,7 @@
         <v>132</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>271</v>
@@ -4758,13 +4770,13 @@
         <v>133</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>251</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E131" s="1"/>
       <c r="F131" s="1"/>
@@ -4778,13 +4790,13 @@
         <v>134</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>253</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>232</v>
@@ -4800,7 +4812,7 @@
         <v>135</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>254</v>
@@ -4820,7 +4832,7 @@
         <v>136</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>265</v>
@@ -4840,13 +4852,13 @@
         <v>137</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>252</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>232</v>
@@ -4862,7 +4874,7 @@
         <v>138</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>247</v>
@@ -4882,13 +4894,13 @@
         <v>139</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>264</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>232</v>
@@ -4904,7 +4916,7 @@
         <v>140</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>257</v>
@@ -4924,13 +4936,13 @@
         <v>141</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>268</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>232</v>
@@ -4946,7 +4958,7 @@
         <v>142</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>247</v>
@@ -4966,7 +4978,7 @@
         <v>143</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>261</v>
@@ -4986,7 +4998,7 @@
         <v>144</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>257</v>
@@ -5006,7 +5018,7 @@
         <v>145</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C143" s="1">
         <v>0</v>
@@ -5026,13 +5038,13 @@
         <v>146</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>249</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>232</v>
@@ -5048,7 +5060,7 @@
         <v>147</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>257</v>
@@ -5068,7 +5080,7 @@
         <v>148</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>257</v>
@@ -5088,7 +5100,7 @@
         <v>149</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>257</v>
@@ -5108,7 +5120,7 @@
         <v>150</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>255</v>
@@ -5128,13 +5140,13 @@
         <v>151</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>255</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>232</v>
@@ -5150,7 +5162,7 @@
         <v>152</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>261</v>
@@ -5170,13 +5182,13 @@
         <v>153</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>264</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>232</v>
@@ -5192,7 +5204,7 @@
         <v>154</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>254</v>
@@ -5214,13 +5226,13 @@
         <v>155</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>251</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E153" s="1"/>
       <c r="F153" s="1"/>
@@ -5234,13 +5246,13 @@
         <v>156</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>251</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E154" s="1"/>
       <c r="F154" s="1"/>
@@ -5254,13 +5266,13 @@
         <v>157</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>259</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>232</v>
@@ -5276,13 +5288,13 @@
         <v>158</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>264</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>232</v>
@@ -5298,7 +5310,7 @@
         <v>159</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>269</v>
@@ -5318,7 +5330,7 @@
         <v>160</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>254</v>
@@ -5340,13 +5352,13 @@
         <v>161</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>259</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>232</v>
@@ -5362,13 +5374,13 @@
         <v>162</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>251</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>232</v>
@@ -5384,13 +5396,13 @@
         <v>163</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>256</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>232</v>
@@ -5406,7 +5418,7 @@
         <v>164</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>262</v>
@@ -5426,7 +5438,7 @@
         <v>165</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>265</v>
@@ -5446,7 +5458,7 @@
         <v>166</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>268</v>
@@ -5468,7 +5480,7 @@
         <v>167</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>254</v>
@@ -5488,7 +5500,7 @@
         <v>168</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>247</v>
@@ -5508,7 +5520,7 @@
         <v>169</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>268</v>
@@ -5528,7 +5540,7 @@
         <v>170</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>254</v>
@@ -5548,7 +5560,7 @@
         <v>171</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>265</v>
@@ -5568,7 +5580,7 @@
         <v>172</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>247</v>
@@ -5588,7 +5600,7 @@
         <v>173</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>252</v>
@@ -5610,13 +5622,13 @@
         <v>174</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>251</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E172" s="1"/>
       <c r="F172" s="1"/>
@@ -5630,7 +5642,7 @@
         <v>175</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>247</v>
@@ -5650,13 +5662,13 @@
         <v>176</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>272</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E174" s="1"/>
       <c r="F174" s="1"/>
@@ -5670,7 +5682,7 @@
         <v>177</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>257</v>
@@ -5690,7 +5702,7 @@
         <v>178</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>257</v>
@@ -5710,13 +5722,13 @@
         <v>179</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>255</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>232</v>
@@ -5732,7 +5744,7 @@
         <v>180</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>259</v>
@@ -5752,13 +5764,13 @@
         <v>181</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>255</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>232</v>
@@ -5774,13 +5786,13 @@
         <v>182</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>264</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>232</v>
@@ -5796,13 +5808,13 @@
         <v>183</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>268</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>232</v>
@@ -5818,13 +5830,13 @@
         <v>184</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>251</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E182" s="1"/>
       <c r="F182" s="1"/>
@@ -5838,13 +5850,13 @@
         <v>185</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>262</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E183" s="1"/>
       <c r="F183" s="1"/>
@@ -5858,7 +5870,7 @@
         <v>186</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>251</v>
@@ -5880,13 +5892,13 @@
         <v>187</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>273</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E185" s="1"/>
       <c r="F185" s="1"/>
@@ -5900,7 +5912,7 @@
         <v>188</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>261</v>
@@ -5920,13 +5932,13 @@
         <v>189</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>251</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>232</v>
@@ -5942,13 +5954,13 @@
         <v>190</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>256</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>232</v>
@@ -5964,7 +5976,7 @@
         <v>191</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>274</v>
@@ -5984,7 +5996,7 @@
         <v>192</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>275</v>
@@ -6004,13 +6016,13 @@
         <v>193</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>508</v>
+        <v>254</v>
       </c>
       <c r="E191" s="1" t="s">
         <v>232</v>
@@ -6026,13 +6038,13 @@
         <v>194</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>256</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>232</v>
@@ -6048,13 +6060,13 @@
         <v>195</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>249</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E193" s="1" t="s">
         <v>232</v>
@@ -6070,13 +6082,13 @@
         <v>196</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>266</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E194" s="1" t="s">
         <v>232</v>
@@ -6092,7 +6104,7 @@
         <v>197</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>247</v>
@@ -6112,7 +6124,7 @@
         <v>198</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>266</v>
@@ -6134,7 +6146,7 @@
         <v>199</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>247</v>
@@ -6154,7 +6166,7 @@
         <v>200</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>262</v>
@@ -6174,13 +6186,13 @@
         <v>201</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>248</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E199" s="1" t="s">
         <v>232</v>
@@ -6196,13 +6208,13 @@
         <v>202</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>264</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E200" s="1" t="s">
         <v>232</v>
@@ -6218,7 +6230,7 @@
         <v>203</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>260</v>
@@ -6238,7 +6250,7 @@
         <v>204</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>247</v>
@@ -6258,13 +6270,13 @@
         <v>205</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>249</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E203" s="1" t="s">
         <v>232</v>
@@ -6280,13 +6292,13 @@
         <v>206</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>249</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E204" s="1" t="s">
         <v>232</v>
@@ -6302,7 +6314,7 @@
         <v>207</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>266</v>
@@ -6324,7 +6336,7 @@
         <v>208</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>262</v>
@@ -6344,13 +6356,13 @@
         <v>209</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>264</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E207" s="1" t="s">
         <v>232</v>
@@ -6366,13 +6378,13 @@
         <v>210</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>266</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E208" s="1" t="s">
         <v>232</v>
@@ -6388,13 +6400,13 @@
         <v>211</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>253</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E209" s="1" t="s">
         <v>232</v>
@@ -6410,13 +6422,13 @@
         <v>212</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>250</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E210" s="1"/>
       <c r="F210" s="1"/>
@@ -6430,13 +6442,13 @@
         <v>213</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>251</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E211" s="1"/>
       <c r="F211" s="1"/>
@@ -6450,7 +6462,7 @@
         <v>214</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>263</v>
@@ -6470,7 +6482,7 @@
         <v>215</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>274</v>
@@ -6490,13 +6502,13 @@
         <v>216</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>256</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E214" s="1" t="s">
         <v>232</v>
@@ -6512,7 +6524,7 @@
         <v>217</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>263</v>
@@ -6532,13 +6544,13 @@
         <v>218</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>268</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E216" s="1" t="s">
         <v>232</v>
@@ -6554,13 +6566,13 @@
         <v>219</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>268</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E217" s="1" t="s">
         <v>232</v>
@@ -6576,7 +6588,7 @@
         <v>220</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>246</v>
@@ -6595,14 +6607,14 @@
       <c r="A219" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B219" s="1">
-        <v>0</v>
-      </c>
-      <c r="C219" s="1">
-        <v>0</v>
-      </c>
-      <c r="D219" s="1">
-        <v>0</v>
+      <c r="B219" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D219" s="1" t="s">
+        <v>247</v>
       </c>
       <c r="E219" s="1"/>
       <c r="F219" s="1"/>
@@ -6615,14 +6627,14 @@
       <c r="A220" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B220" s="1">
-        <v>0</v>
-      </c>
-      <c r="C220" s="1">
-        <v>0</v>
-      </c>
-      <c r="D220" s="1">
-        <v>0</v>
+      <c r="B220" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D220" s="1" t="s">
+        <v>510</v>
       </c>
       <c r="E220" s="1"/>
       <c r="F220" s="1"/>
@@ -7452,7 +7464,7 @@
         <v>302</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
@@ -9866,7 +9878,7 @@
         <v>347</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D59" s="1">
         <v>0</v>
@@ -12160,7 +12172,7 @@
         <v>390</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="D102" s="1">
         <v>0</v>
@@ -12462,7 +12474,7 @@
         <v>395</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D107" s="1">
         <v>0</v>
@@ -12634,8 +12646,8 @@
       <c r="A110" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>398</v>
+      <c r="B110" s="1" t="e">
+        <v>#N/A</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>247</v>
@@ -12677,7 +12689,7 @@
         <v>113</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>246</v>
@@ -12719,7 +12731,7 @@
         <v>114</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>251</v>
@@ -12761,7 +12773,7 @@
         <v>115</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>251</v>
@@ -12803,7 +12815,7 @@
         <v>116</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>254</v>
@@ -12845,7 +12857,7 @@
         <v>117</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>259</v>
@@ -12929,7 +12941,7 @@
         <v>118</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>269</v>
@@ -12971,7 +12983,7 @@
         <v>119</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>261</v>
@@ -13013,7 +13025,7 @@
         <v>120</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>258</v>
@@ -13055,7 +13067,7 @@
         <v>121</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>260</v>
@@ -13097,7 +13109,7 @@
         <v>122</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>269</v>
@@ -13139,7 +13151,7 @@
         <v>123</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>255</v>
@@ -13217,7 +13229,7 @@
         <v>124</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>265</v>
@@ -13259,7 +13271,7 @@
         <v>125</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>270</v>
@@ -13301,7 +13313,7 @@
         <v>126</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>270</v>
@@ -13343,7 +13355,7 @@
         <v>127</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>265</v>
@@ -13385,7 +13397,7 @@
         <v>128</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>256</v>
@@ -13465,7 +13477,7 @@
         <v>129</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>254</v>
@@ -13507,7 +13519,7 @@
         <v>130</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>251</v>
@@ -13549,7 +13561,7 @@
         <v>131</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>250</v>
@@ -13591,7 +13603,7 @@
         <v>132</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>271</v>
@@ -13633,7 +13645,7 @@
         <v>133</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>251</v>
@@ -13675,7 +13687,7 @@
         <v>134</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>253</v>
@@ -13759,7 +13771,7 @@
         <v>135</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>254</v>
@@ -13801,7 +13813,7 @@
         <v>136</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>265</v>
@@ -13843,7 +13855,7 @@
         <v>137</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>252</v>
@@ -13913,7 +13925,7 @@
         <v>138</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>247</v>
@@ -13955,7 +13967,7 @@
         <v>139</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>264</v>
@@ -14033,7 +14045,7 @@
         <v>140</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>257</v>
@@ -14075,7 +14087,7 @@
         <v>141</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>268</v>
@@ -14159,7 +14171,7 @@
         <v>142</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>247</v>
@@ -14201,7 +14213,7 @@
         <v>143</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>261</v>
@@ -14243,7 +14255,7 @@
         <v>144</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>257</v>
@@ -14285,7 +14297,7 @@
         <v>145</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C143" s="1">
         <v>0</v>
@@ -14327,7 +14339,7 @@
         <v>146</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>249</v>
@@ -14411,7 +14423,7 @@
         <v>147</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>257</v>
@@ -14453,7 +14465,7 @@
         <v>148</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>257</v>
@@ -14495,7 +14507,7 @@
         <v>149</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>257</v>
@@ -14537,7 +14549,7 @@
         <v>150</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>255</v>
@@ -14579,7 +14591,7 @@
         <v>151</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>255</v>
@@ -14663,7 +14675,7 @@
         <v>152</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>261</v>
@@ -14705,7 +14717,7 @@
         <v>153</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>264</v>
@@ -14773,7 +14785,7 @@
         <v>154</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>254</v>
@@ -14815,7 +14827,7 @@
         <v>155</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>251</v>
@@ -14857,7 +14869,7 @@
         <v>156</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>251</v>
@@ -14899,7 +14911,7 @@
         <v>157</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>259</v>
@@ -14967,7 +14979,7 @@
         <v>158</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>264</v>
@@ -15009,7 +15021,7 @@
         <v>159</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>269</v>
@@ -15051,7 +15063,7 @@
         <v>160</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>254</v>
@@ -15093,7 +15105,7 @@
         <v>161</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>259</v>
@@ -15175,7 +15187,7 @@
         <v>162</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>251</v>
@@ -15217,7 +15229,7 @@
         <v>163</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>256</v>
@@ -15297,7 +15309,7 @@
         <v>164</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>262</v>
@@ -15339,7 +15351,7 @@
         <v>165</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>265</v>
@@ -15381,7 +15393,7 @@
         <v>166</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>268</v>
@@ -15423,7 +15435,7 @@
         <v>167</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>254</v>
@@ -15465,7 +15477,7 @@
         <v>168</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>247</v>
@@ -15507,7 +15519,7 @@
         <v>169</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>268</v>
@@ -15549,7 +15561,7 @@
         <v>170</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>254</v>
@@ -15591,7 +15603,7 @@
         <v>171</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>265</v>
@@ -15633,7 +15645,7 @@
         <v>172</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>247</v>
@@ -15675,7 +15687,7 @@
         <v>173</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>252</v>
@@ -15717,7 +15729,7 @@
         <v>174</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>251</v>
@@ -15759,7 +15771,7 @@
         <v>175</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>247</v>
@@ -15801,7 +15813,7 @@
         <v>176</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>272</v>
@@ -15843,7 +15855,7 @@
         <v>177</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>257</v>
@@ -15885,7 +15897,7 @@
         <v>178</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>257</v>
@@ -15927,7 +15939,7 @@
         <v>179</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>255</v>
@@ -16013,7 +16025,7 @@
         <v>180</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>259</v>
@@ -16055,7 +16067,7 @@
         <v>181</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>255</v>
@@ -16125,7 +16137,7 @@
         <v>182</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>264</v>
@@ -16203,7 +16215,7 @@
         <v>183</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>268</v>
@@ -16275,7 +16287,7 @@
         <v>184</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>251</v>
@@ -16317,7 +16329,7 @@
         <v>185</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>262</v>
@@ -16359,7 +16371,7 @@
         <v>186</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>251</v>
@@ -16401,7 +16413,7 @@
         <v>187</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>273</v>
@@ -16443,7 +16455,7 @@
         <v>188</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>261</v>
@@ -16485,7 +16497,7 @@
         <v>189</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>251</v>
@@ -16527,7 +16539,7 @@
         <v>190</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>256</v>
@@ -16607,7 +16619,7 @@
         <v>191</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>274</v>
@@ -16649,7 +16661,7 @@
         <v>192</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>275</v>
@@ -16691,10 +16703,10 @@
         <v>193</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D191" s="1">
         <v>21</v>
@@ -16775,7 +16787,7 @@
         <v>194</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>256</v>
@@ -16861,7 +16873,7 @@
         <v>195</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>249</v>
@@ -16933,7 +16945,7 @@
         <v>196</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>266</v>
@@ -16975,7 +16987,7 @@
         <v>197</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>247</v>
@@ -17017,7 +17029,7 @@
         <v>198</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>266</v>
@@ -17059,7 +17071,7 @@
         <v>199</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>247</v>
@@ -17101,7 +17113,7 @@
         <v>200</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>262</v>
@@ -17143,7 +17155,7 @@
         <v>201</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>248</v>
@@ -17235,7 +17247,7 @@
         <v>202</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>264</v>
@@ -17319,7 +17331,7 @@
         <v>203</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>260</v>
@@ -17361,7 +17373,7 @@
         <v>204</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>247</v>
@@ -17403,7 +17415,7 @@
         <v>205</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>249</v>
@@ -17487,7 +17499,7 @@
         <v>206</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>249</v>
@@ -17565,7 +17577,7 @@
         <v>207</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>266</v>
@@ -17607,7 +17619,7 @@
         <v>208</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>262</v>
@@ -17649,7 +17661,7 @@
         <v>209</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>264</v>
@@ -17707,7 +17719,7 @@
         <v>210</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>266</v>
@@ -17777,7 +17789,7 @@
         <v>211</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>253</v>
@@ -17861,7 +17873,7 @@
         <v>212</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>250</v>
@@ -17903,7 +17915,7 @@
         <v>213</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>251</v>
@@ -17945,7 +17957,7 @@
         <v>214</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>263</v>
@@ -17987,7 +17999,7 @@
         <v>215</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>274</v>
@@ -18029,7 +18041,7 @@
         <v>216</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>256</v>
@@ -18107,7 +18119,7 @@
         <v>217</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>263</v>
@@ -18149,7 +18161,7 @@
         <v>218</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>268</v>
@@ -18233,7 +18245,7 @@
         <v>219</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>268</v>
@@ -18317,7 +18329,7 @@
         <v>220</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>246</v>
@@ -18358,11 +18370,11 @@
       <c r="A219" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B219" s="1">
-        <v>0</v>
-      </c>
-      <c r="C219" s="1">
-        <v>0</v>
+      <c r="B219" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>247</v>
       </c>
       <c r="D219" s="1">
         <v>0</v>
@@ -18400,14 +18412,14 @@
       <c r="A220" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B220" s="1">
-        <v>0</v>
-      </c>
-      <c r="C220" s="1">
-        <v>0</v>
+      <c r="B220" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>266</v>
       </c>
       <c r="D220" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E220" s="6"/>
       <c r="F220" s="6"/>
@@ -18426,7 +18438,9 @@
       <c r="S220" s="6"/>
       <c r="T220" s="6"/>
       <c r="U220" s="6"/>
-      <c r="V220" s="6"/>
+      <c r="V220" s="11">
+        <v>46301</v>
+      </c>
       <c r="W220" s="6"/>
       <c r="X220" s="6"/>
       <c r="Y220" s="6"/>
